--- a/Bibsam_tidskriftslistor/scifree_data_gruyter.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_gruyter.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60F0071-F460-462D-AD72-0BB160881822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2951B0B4-9997-4A83-B144-4F05494BA069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{555F2B57-0DE3-44F7-85C6-A70D37746D81}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2516" uniqueCount="1244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2545" uniqueCount="1259">
   <si>
     <t>Imprint</t>
   </si>
@@ -1613,12 +1613,6 @@
     <t>Noise Mapping</t>
   </si>
   <si>
-    <t>2353-0626</t>
-  </si>
-  <si>
-    <t>Nonautonomous Dynamical Systems</t>
-  </si>
-  <si>
     <t>2192-8029</t>
   </si>
   <si>
@@ -3647,9 +3641,6 @@
     <t>https://www.degruyterbrill.com/noise</t>
   </si>
   <si>
-    <t>https://www.degruyterbrill.com/msds</t>
-  </si>
-  <si>
     <t>https://www.degruyterbrill.com/nleng</t>
   </si>
   <si>
@@ -3768,6 +3759,60 @@
   </si>
   <si>
     <t>https://www.degruyterbrill.com/zfmw</t>
+  </si>
+  <si>
+    <t>2300-0929</t>
+  </si>
+  <si>
+    <t>AUTEX Research Journal</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/aut/html</t>
+  </si>
+  <si>
+    <t>2160-5068</t>
+  </si>
+  <si>
+    <t>Chinese Archaeology</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/char/html</t>
+  </si>
+  <si>
+    <t>2569-1589</t>
+  </si>
+  <si>
+    <t>Die Denkmalpflege</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/dkp/html</t>
+  </si>
+  <si>
+    <t>2942-4402</t>
+  </si>
+  <si>
+    <t>Gender and Sustainability in the Global South</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/gsgs/html</t>
+  </si>
+  <si>
+    <t>2942-738X</t>
+  </si>
+  <si>
+    <t>Global Medical Education</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/gme/html</t>
+  </si>
+  <si>
+    <t>2942-769X</t>
+  </si>
+  <si>
+    <t>Journal of Integrated Global STEM</t>
+  </si>
+  <si>
+    <t>https://www.degruyterbrill.com/journal/key/jigs/html</t>
   </si>
 </sst>
 </file>
@@ -3823,19 +3868,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2B6AE563-A31B-438C-9DDA-FCBD69F1AB42}" name="Table1" displayName="Table1" ref="A1:G410" totalsRowShown="0">
-  <autoFilter ref="A1:G410" xr:uid="{2B6AE563-A31B-438C-9DDA-FCBD69F1AB42}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G410">
-    <sortCondition ref="F1:F410"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A539647A-7C2F-44D2-9732-F0FDDA6FCFFD}" name="Table2" displayName="Table2" ref="A1:G415" totalsRowShown="0">
+  <autoFilter ref="A1:G415" xr:uid="{A539647A-7C2F-44D2-9732-F0FDDA6FCFFD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G415">
+    <sortCondition ref="D1:D415"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{84F2B61E-4B58-4BCC-A38E-188187874230}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{FB4E6E7A-20C6-4135-9BB9-2DEEC08C8A6B}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{05C534A4-EE10-41DE-83B9-C557C02C8B92}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{3567B7A9-AD3E-4762-B873-34657748F8E5}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{8E92C3D7-48BE-499C-B282-FD3D2F41F9DB}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{5D0B990C-3180-4ABF-874D-DFFCB74D6292}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{99A8A8B3-AFA0-4BBC-BAB0-BC48961006B8}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{4F4751C8-FA1A-4450-BAA4-08B04515376C}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{324CA29D-EAA3-4C5A-B34C-D642B836B1A4}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{6C55EB2A-B121-4011-A965-DA7D624EBE29}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{355FD98C-880F-42E4-A030-9E64A02C8ECD}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{CB98BB49-52F2-41C2-8478-54BB5BD19FE4}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{DEC21385-C16C-418B-B205-37ED39C5ECEF}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{1889493C-A044-4CAD-8557-E52FDCC1EA37}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4137,14 +4182,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD35B3D-85BE-4343-811C-6208C2631C0E}">
-  <dimension ref="A1:G410"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{561717F2-C306-477B-8009-762A607C0EC6}">
+  <dimension ref="A1:G415"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="39.85546875" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
@@ -4184,7 +4229,7 @@
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -4204,7 +4249,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
@@ -4218,16 +4263,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>843</v>
+        <v>1127</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -4238,13 +4283,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -4255,16 +4300,16 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -4275,19 +4320,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>846</v>
+        <v>1128</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -4295,19 +4343,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>847</v>
+        <v>1129</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -4315,16 +4363,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
@@ -4335,16 +4383,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="F10" t="s">
         <v>10</v>
@@ -4355,16 +4403,16 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="F11" t="s">
         <v>10</v>
@@ -4378,16 +4426,19 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>851</v>
+        <v>1130</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -4395,19 +4446,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>852</v>
+        <v>1131</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -4415,16 +4466,16 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="F14" t="s">
         <v>10</v>
@@ -4438,13 +4489,13 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E15" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="F15" t="s">
         <v>10</v>
@@ -4458,13 +4509,13 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="F16" t="s">
         <v>10</v>
@@ -4478,13 +4529,13 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="F17" t="s">
         <v>10</v>
@@ -4495,16 +4546,16 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="F18" t="s">
         <v>10</v>
@@ -4518,16 +4569,19 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s">
-        <v>858</v>
+        <v>1132</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -4535,16 +4589,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="F20" t="s">
         <v>10</v>
@@ -4558,13 +4612,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="F21" t="s">
         <v>10</v>
@@ -4578,13 +4632,13 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="F22" t="s">
         <v>10</v>
@@ -4595,16 +4649,16 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E23" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="F23" t="s">
         <v>10</v>
@@ -4618,13 +4672,13 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="F24" t="s">
         <v>10</v>
@@ -4638,13 +4692,13 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E25" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="F25" t="s">
         <v>10</v>
@@ -4658,13 +4712,13 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E26" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="F26" t="s">
         <v>10</v>
@@ -4678,13 +4732,13 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E27" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="F27" t="s">
         <v>10</v>
@@ -4695,19 +4749,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
-        <v>867</v>
+        <v>1133</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
@@ -4718,13 +4772,13 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="F29" t="s">
         <v>10</v>
@@ -4738,16 +4792,19 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>809</v>
+      </c>
+      <c r="C30" t="s">
+        <v>810</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>811</v>
       </c>
       <c r="E30" t="s">
-        <v>869</v>
+        <v>1134</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G30" t="s">
         <v>11</v>
@@ -4755,16 +4812,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>870</v>
+        <v>860</v>
       </c>
       <c r="F31" t="s">
         <v>10</v>
@@ -4778,16 +4835,16 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>1241</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>1242</v>
       </c>
       <c r="E32" t="s">
-        <v>871</v>
+        <v>1243</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
@@ -4798,13 +4855,13 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="E33" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="F33" t="s">
         <v>10</v>
@@ -4815,16 +4872,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>873</v>
+        <v>862</v>
       </c>
       <c r="F34" t="s">
         <v>10</v>
@@ -4838,13 +4895,13 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="E35" t="s">
-        <v>874</v>
+        <v>863</v>
       </c>
       <c r="F35" t="s">
         <v>10</v>
@@ -4855,16 +4912,16 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E36" t="s">
-        <v>875</v>
+        <v>864</v>
       </c>
       <c r="F36" t="s">
         <v>10</v>
@@ -4875,16 +4932,16 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="E37" t="s">
-        <v>876</v>
+        <v>865</v>
       </c>
       <c r="F37" t="s">
         <v>10</v>
@@ -4895,16 +4952,16 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="E38" t="s">
-        <v>877</v>
+        <v>866</v>
       </c>
       <c r="F38" t="s">
         <v>10</v>
@@ -4918,13 +4975,13 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="E39" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -4935,19 +4992,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="D40" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="E40" t="s">
-        <v>879</v>
+        <v>1135</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -4958,13 +5015,13 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="E41" t="s">
-        <v>880</v>
+        <v>868</v>
       </c>
       <c r="F41" t="s">
         <v>10</v>
@@ -4975,16 +5032,16 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="D42" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="E42" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="F42" t="s">
         <v>10</v>
@@ -4998,16 +5055,16 @@
         <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="D43" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="E43" t="s">
-        <v>882</v>
+        <v>1136</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
         <v>11</v>
@@ -5018,13 +5075,13 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="D44" t="s">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="E44" t="s">
-        <v>883</v>
+        <v>870</v>
       </c>
       <c r="F44" t="s">
         <v>10</v>
@@ -5038,16 +5095,19 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>156</v>
+        <v>100</v>
+      </c>
+      <c r="C45" t="s">
+        <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="E45" t="s">
-        <v>884</v>
+        <v>1137</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G45" t="s">
         <v>11</v>
@@ -5055,19 +5115,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="D46" t="s">
-        <v>159</v>
+        <v>103</v>
       </c>
       <c r="E46" t="s">
-        <v>885</v>
+        <v>1138</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
         <v>11</v>
@@ -5078,16 +5138,16 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="D47" t="s">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="E47" t="s">
-        <v>886</v>
+        <v>1139</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G47" t="s">
         <v>11</v>
@@ -5098,16 +5158,16 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>164</v>
+        <v>1244</v>
       </c>
       <c r="D48" t="s">
-        <v>165</v>
+        <v>1245</v>
       </c>
       <c r="E48" t="s">
-        <v>887</v>
+        <v>1246</v>
       </c>
       <c r="F48" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
@@ -5115,16 +5175,16 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>170</v>
+        <v>106</v>
       </c>
       <c r="D49" t="s">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="E49" t="s">
-        <v>888</v>
+        <v>871</v>
       </c>
       <c r="F49" t="s">
         <v>10</v>
@@ -5135,19 +5195,19 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>108</v>
       </c>
       <c r="D50" t="s">
-        <v>173</v>
+        <v>109</v>
       </c>
       <c r="E50" t="s">
-        <v>889</v>
+        <v>1140</v>
       </c>
       <c r="F50" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
@@ -5158,16 +5218,16 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>174</v>
+        <v>110</v>
       </c>
       <c r="D51" t="s">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="E51" t="s">
-        <v>890</v>
+        <v>1141</v>
       </c>
       <c r="F51" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
@@ -5175,19 +5235,19 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>178</v>
+        <v>112</v>
       </c>
       <c r="D52" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="E52" t="s">
-        <v>891</v>
+        <v>1142</v>
       </c>
       <c r="F52" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -5198,13 +5258,13 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="D53" t="s">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="E53" t="s">
-        <v>892</v>
+        <v>872</v>
       </c>
       <c r="F53" t="s">
         <v>10</v>
@@ -5215,16 +5275,16 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>185</v>
+        <v>117</v>
       </c>
       <c r="E54" t="s">
-        <v>893</v>
+        <v>873</v>
       </c>
       <c r="F54" t="s">
         <v>10</v>
@@ -5235,16 +5295,16 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>186</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>187</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
-        <v>894</v>
+        <v>874</v>
       </c>
       <c r="F55" t="s">
         <v>10</v>
@@ -5258,13 +5318,13 @@
         <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>188</v>
+        <v>120</v>
       </c>
       <c r="D56" t="s">
-        <v>189</v>
+        <v>121</v>
       </c>
       <c r="E56" t="s">
-        <v>895</v>
+        <v>875</v>
       </c>
       <c r="F56" t="s">
         <v>10</v>
@@ -5278,16 +5338,16 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>190</v>
+        <v>122</v>
       </c>
       <c r="D57" t="s">
-        <v>191</v>
+        <v>123</v>
       </c>
       <c r="E57" t="s">
-        <v>896</v>
+        <v>1143</v>
       </c>
       <c r="F57" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -5298,16 +5358,19 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>192</v>
+        <v>124</v>
+      </c>
+      <c r="C58" t="s">
+        <v>23</v>
       </c>
       <c r="D58" t="s">
-        <v>193</v>
+        <v>125</v>
       </c>
       <c r="E58" t="s">
-        <v>897</v>
+        <v>1144</v>
       </c>
       <c r="F58" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -5318,16 +5381,19 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>194</v>
+        <v>126</v>
+      </c>
+      <c r="C59" t="s">
+        <v>23</v>
       </c>
       <c r="D59" t="s">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="E59" t="s">
-        <v>898</v>
+        <v>1145</v>
       </c>
       <c r="F59" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
@@ -5338,13 +5404,13 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="D60" t="s">
-        <v>197</v>
+        <v>129</v>
       </c>
       <c r="E60" t="s">
-        <v>899</v>
+        <v>876</v>
       </c>
       <c r="F60" t="s">
         <v>10</v>
@@ -5358,16 +5424,19 @@
         <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>198</v>
+        <v>130</v>
+      </c>
+      <c r="C61" t="s">
+        <v>23</v>
       </c>
       <c r="D61" t="s">
-        <v>199</v>
+        <v>131</v>
       </c>
       <c r="E61" t="s">
-        <v>900</v>
+        <v>1146</v>
       </c>
       <c r="F61" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -5378,13 +5447,13 @@
         <v>48</v>
       </c>
       <c r="B62" t="s">
-        <v>200</v>
+        <v>132</v>
       </c>
       <c r="D62" t="s">
-        <v>201</v>
+        <v>133</v>
       </c>
       <c r="E62" t="s">
-        <v>901</v>
+        <v>877</v>
       </c>
       <c r="F62" t="s">
         <v>10</v>
@@ -5395,19 +5464,19 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>202</v>
+        <v>812</v>
       </c>
       <c r="D63" t="s">
-        <v>203</v>
+        <v>813</v>
       </c>
       <c r="E63" t="s">
-        <v>902</v>
+        <v>1147</v>
       </c>
       <c r="F63" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G63" t="s">
         <v>11</v>
@@ -5418,16 +5487,16 @@
         <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>204</v>
+        <v>134</v>
       </c>
       <c r="D64" t="s">
-        <v>205</v>
+        <v>135</v>
       </c>
       <c r="E64" t="s">
-        <v>903</v>
+        <v>1148</v>
       </c>
       <c r="F64" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
@@ -5438,16 +5507,16 @@
         <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>206</v>
+        <v>814</v>
       </c>
       <c r="D65" t="s">
-        <v>207</v>
+        <v>815</v>
       </c>
       <c r="E65" t="s">
-        <v>904</v>
+        <v>1149</v>
       </c>
       <c r="F65" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G65" t="s">
         <v>11</v>
@@ -5458,16 +5527,16 @@
         <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="D66" t="s">
-        <v>209</v>
+        <v>137</v>
       </c>
       <c r="E66" t="s">
-        <v>905</v>
+        <v>1150</v>
       </c>
       <c r="F66" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -5475,19 +5544,22 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>210</v>
+        <v>138</v>
+      </c>
+      <c r="C67" t="s">
+        <v>23</v>
       </c>
       <c r="D67" t="s">
-        <v>211</v>
+        <v>139</v>
       </c>
       <c r="E67" t="s">
-        <v>906</v>
+        <v>1151</v>
       </c>
       <c r="F67" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
@@ -5498,16 +5570,19 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>212</v>
+        <v>140</v>
+      </c>
+      <c r="C68" t="s">
+        <v>23</v>
       </c>
       <c r="D68" t="s">
-        <v>213</v>
+        <v>141</v>
       </c>
       <c r="E68" t="s">
-        <v>907</v>
+        <v>1141</v>
       </c>
       <c r="F68" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -5518,16 +5593,19 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>214</v>
+        <v>142</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
       </c>
       <c r="D69" t="s">
-        <v>215</v>
+        <v>143</v>
       </c>
       <c r="E69" t="s">
-        <v>908</v>
+        <v>1152</v>
       </c>
       <c r="F69" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -5538,16 +5616,19 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>216</v>
+        <v>144</v>
+      </c>
+      <c r="C70" t="s">
+        <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>217</v>
+        <v>145</v>
       </c>
       <c r="E70" t="s">
-        <v>909</v>
+        <v>1153</v>
       </c>
       <c r="F70" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -5558,13 +5639,13 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="D71" t="s">
-        <v>219</v>
+        <v>147</v>
       </c>
       <c r="E71" t="s">
-        <v>910</v>
+        <v>878</v>
       </c>
       <c r="F71" t="s">
         <v>10</v>
@@ -5575,16 +5656,16 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>220</v>
+        <v>148</v>
       </c>
       <c r="D72" t="s">
-        <v>221</v>
+        <v>149</v>
       </c>
       <c r="E72" t="s">
-        <v>911</v>
+        <v>879</v>
       </c>
       <c r="F72" t="s">
         <v>10</v>
@@ -5595,16 +5676,16 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>222</v>
+        <v>150</v>
       </c>
       <c r="D73" t="s">
-        <v>223</v>
+        <v>151</v>
       </c>
       <c r="E73" t="s">
-        <v>912</v>
+        <v>880</v>
       </c>
       <c r="F73" t="s">
         <v>10</v>
@@ -5615,16 +5696,16 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B74" t="s">
-        <v>230</v>
+        <v>152</v>
       </c>
       <c r="D74" t="s">
-        <v>231</v>
+        <v>153</v>
       </c>
       <c r="E74" t="s">
-        <v>913</v>
+        <v>881</v>
       </c>
       <c r="F74" t="s">
         <v>10</v>
@@ -5638,16 +5719,16 @@
         <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>232</v>
+        <v>154</v>
       </c>
       <c r="D75" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="E75" t="s">
-        <v>914</v>
+        <v>1154</v>
       </c>
       <c r="F75" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G75" t="s">
         <v>11</v>
@@ -5658,13 +5739,13 @@
         <v>7</v>
       </c>
       <c r="B76" t="s">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="D76" t="s">
-        <v>235</v>
+        <v>157</v>
       </c>
       <c r="E76" t="s">
-        <v>915</v>
+        <v>882</v>
       </c>
       <c r="F76" t="s">
         <v>10</v>
@@ -5675,16 +5756,16 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B77" t="s">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="D77" t="s">
-        <v>237</v>
+        <v>159</v>
       </c>
       <c r="E77" t="s">
-        <v>916</v>
+        <v>883</v>
       </c>
       <c r="F77" t="s">
         <v>10</v>
@@ -5698,16 +5779,16 @@
         <v>7</v>
       </c>
       <c r="B78" t="s">
-        <v>240</v>
+        <v>1247</v>
       </c>
       <c r="D78" t="s">
-        <v>241</v>
+        <v>1248</v>
       </c>
       <c r="E78" t="s">
-        <v>917</v>
+        <v>1249</v>
       </c>
       <c r="F78" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G78" t="s">
         <v>11</v>
@@ -5715,19 +5796,19 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>242</v>
+        <v>816</v>
       </c>
       <c r="D79" t="s">
-        <v>243</v>
+        <v>817</v>
       </c>
       <c r="E79" t="s">
-        <v>918</v>
+        <v>1155</v>
       </c>
       <c r="F79" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G79" t="s">
         <v>11</v>
@@ -5738,16 +5819,16 @@
         <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>244</v>
+        <v>160</v>
       </c>
       <c r="D80" t="s">
-        <v>245</v>
+        <v>161</v>
       </c>
       <c r="E80" t="s">
-        <v>919</v>
+        <v>1156</v>
       </c>
       <c r="F80" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G80" t="s">
         <v>11</v>
@@ -5758,13 +5839,13 @@
         <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>246</v>
+        <v>162</v>
       </c>
       <c r="D81" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
       <c r="E81" t="s">
-        <v>920</v>
+        <v>884</v>
       </c>
       <c r="F81" t="s">
         <v>10</v>
@@ -5778,13 +5859,13 @@
         <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="D82" t="s">
-        <v>251</v>
+        <v>165</v>
       </c>
       <c r="E82" t="s">
-        <v>921</v>
+        <v>885</v>
       </c>
       <c r="F82" t="s">
         <v>10</v>
@@ -5795,19 +5876,19 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>252</v>
+        <v>166</v>
       </c>
       <c r="D83" t="s">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="E83" t="s">
-        <v>922</v>
+        <v>1157</v>
       </c>
       <c r="F83" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G83" t="s">
         <v>11</v>
@@ -5818,16 +5899,16 @@
         <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="D84" t="s">
-        <v>255</v>
+        <v>169</v>
       </c>
       <c r="E84" t="s">
-        <v>923</v>
+        <v>1158</v>
       </c>
       <c r="F84" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G84" t="s">
         <v>11</v>
@@ -5835,16 +5916,16 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B85" t="s">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="D85" t="s">
-        <v>261</v>
+        <v>171</v>
       </c>
       <c r="E85" t="s">
-        <v>924</v>
+        <v>886</v>
       </c>
       <c r="F85" t="s">
         <v>10</v>
@@ -5855,16 +5936,16 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>266</v>
+        <v>172</v>
       </c>
       <c r="D86" t="s">
-        <v>267</v>
+        <v>173</v>
       </c>
       <c r="E86" t="s">
-        <v>925</v>
+        <v>887</v>
       </c>
       <c r="F86" t="s">
         <v>10</v>
@@ -5878,13 +5959,13 @@
         <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>268</v>
+        <v>174</v>
       </c>
       <c r="D87" t="s">
-        <v>269</v>
+        <v>175</v>
       </c>
       <c r="E87" t="s">
-        <v>926</v>
+        <v>888</v>
       </c>
       <c r="F87" t="s">
         <v>10</v>
@@ -5895,19 +5976,19 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>272</v>
+        <v>176</v>
       </c>
       <c r="D88" t="s">
-        <v>273</v>
+        <v>177</v>
       </c>
       <c r="E88" t="s">
-        <v>927</v>
+        <v>1159</v>
       </c>
       <c r="F88" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
@@ -5918,13 +5999,13 @@
         <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>274</v>
+        <v>178</v>
       </c>
       <c r="D89" t="s">
-        <v>275</v>
+        <v>179</v>
       </c>
       <c r="E89" t="s">
-        <v>928</v>
+        <v>889</v>
       </c>
       <c r="F89" t="s">
         <v>10</v>
@@ -5935,16 +6016,16 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>276</v>
+        <v>180</v>
       </c>
       <c r="D90" t="s">
-        <v>277</v>
+        <v>181</v>
       </c>
       <c r="E90" t="s">
-        <v>929</v>
+        <v>890</v>
       </c>
       <c r="F90" t="s">
         <v>10</v>
@@ -5958,16 +6039,19 @@
         <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>278</v>
+        <v>182</v>
+      </c>
+      <c r="C91" t="s">
+        <v>23</v>
       </c>
       <c r="D91" t="s">
-        <v>279</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>930</v>
+        <v>1160</v>
       </c>
       <c r="F91" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G91" t="s">
         <v>11</v>
@@ -5978,13 +6062,13 @@
         <v>7</v>
       </c>
       <c r="B92" t="s">
-        <v>280</v>
+        <v>184</v>
       </c>
       <c r="D92" t="s">
-        <v>281</v>
+        <v>185</v>
       </c>
       <c r="E92" t="s">
-        <v>931</v>
+        <v>891</v>
       </c>
       <c r="F92" t="s">
         <v>10</v>
@@ -5998,13 +6082,13 @@
         <v>7</v>
       </c>
       <c r="B93" t="s">
-        <v>282</v>
+        <v>186</v>
       </c>
       <c r="D93" t="s">
-        <v>283</v>
+        <v>187</v>
       </c>
       <c r="E93" t="s">
-        <v>932</v>
+        <v>892</v>
       </c>
       <c r="F93" t="s">
         <v>10</v>
@@ -6018,13 +6102,13 @@
         <v>48</v>
       </c>
       <c r="B94" t="s">
-        <v>284</v>
+        <v>188</v>
       </c>
       <c r="D94" t="s">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="E94" t="s">
-        <v>933</v>
+        <v>893</v>
       </c>
       <c r="F94" t="s">
         <v>10</v>
@@ -6038,13 +6122,13 @@
         <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>286</v>
+        <v>190</v>
       </c>
       <c r="D95" t="s">
-        <v>287</v>
+        <v>191</v>
       </c>
       <c r="E95" t="s">
-        <v>934</v>
+        <v>894</v>
       </c>
       <c r="F95" t="s">
         <v>10</v>
@@ -6058,13 +6142,13 @@
         <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>288</v>
+        <v>192</v>
       </c>
       <c r="D96" t="s">
-        <v>289</v>
+        <v>193</v>
       </c>
       <c r="E96" t="s">
-        <v>935</v>
+        <v>895</v>
       </c>
       <c r="F96" t="s">
         <v>10</v>
@@ -6075,16 +6159,16 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>290</v>
+        <v>194</v>
       </c>
       <c r="D97" t="s">
-        <v>291</v>
+        <v>195</v>
       </c>
       <c r="E97" t="s">
-        <v>936</v>
+        <v>896</v>
       </c>
       <c r="F97" t="s">
         <v>10</v>
@@ -6095,16 +6179,16 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>292</v>
+        <v>196</v>
       </c>
       <c r="D98" t="s">
-        <v>293</v>
+        <v>197</v>
       </c>
       <c r="E98" t="s">
-        <v>937</v>
+        <v>897</v>
       </c>
       <c r="F98" t="s">
         <v>10</v>
@@ -6118,13 +6202,13 @@
         <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>294</v>
+        <v>198</v>
       </c>
       <c r="D99" t="s">
-        <v>295</v>
+        <v>199</v>
       </c>
       <c r="E99" t="s">
-        <v>938</v>
+        <v>898</v>
       </c>
       <c r="F99" t="s">
         <v>10</v>
@@ -6135,19 +6219,19 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>296</v>
+        <v>818</v>
       </c>
       <c r="D100" t="s">
-        <v>297</v>
+        <v>819</v>
       </c>
       <c r="E100" t="s">
-        <v>939</v>
+        <v>1161</v>
       </c>
       <c r="F100" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
@@ -6155,16 +6239,16 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B101" t="s">
-        <v>298</v>
+        <v>200</v>
       </c>
       <c r="D101" t="s">
-        <v>299</v>
+        <v>201</v>
       </c>
       <c r="E101" t="s">
-        <v>940</v>
+        <v>899</v>
       </c>
       <c r="F101" t="s">
         <v>10</v>
@@ -6175,16 +6259,16 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B102" t="s">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="D102" t="s">
-        <v>301</v>
+        <v>203</v>
       </c>
       <c r="E102" t="s">
-        <v>941</v>
+        <v>900</v>
       </c>
       <c r="F102" t="s">
         <v>10</v>
@@ -6198,13 +6282,13 @@
         <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>302</v>
+        <v>204</v>
       </c>
       <c r="D103" t="s">
-        <v>303</v>
+        <v>205</v>
       </c>
       <c r="E103" t="s">
-        <v>942</v>
+        <v>901</v>
       </c>
       <c r="F103" t="s">
         <v>10</v>
@@ -6218,13 +6302,13 @@
         <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="D104" t="s">
-        <v>305</v>
+        <v>207</v>
       </c>
       <c r="E104" t="s">
-        <v>943</v>
+        <v>902</v>
       </c>
       <c r="F104" t="s">
         <v>10</v>
@@ -6238,13 +6322,13 @@
         <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>306</v>
+        <v>208</v>
       </c>
       <c r="D105" t="s">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="E105" t="s">
-        <v>944</v>
+        <v>903</v>
       </c>
       <c r="F105" t="s">
         <v>10</v>
@@ -6255,19 +6339,19 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>308</v>
+        <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>309</v>
+        <v>820</v>
       </c>
       <c r="D106" t="s">
-        <v>310</v>
+        <v>821</v>
       </c>
       <c r="E106" t="s">
-        <v>945</v>
+        <v>1162</v>
       </c>
       <c r="F106" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
@@ -6275,16 +6359,16 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>311</v>
+        <v>210</v>
       </c>
       <c r="D107" t="s">
-        <v>312</v>
+        <v>211</v>
       </c>
       <c r="E107" t="s">
-        <v>946</v>
+        <v>904</v>
       </c>
       <c r="F107" t="s">
         <v>10</v>
@@ -6298,13 +6382,13 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>313</v>
+        <v>212</v>
       </c>
       <c r="D108" t="s">
-        <v>314</v>
+        <v>213</v>
       </c>
       <c r="E108" t="s">
-        <v>947</v>
+        <v>905</v>
       </c>
       <c r="F108" t="s">
         <v>10</v>
@@ -6318,16 +6402,16 @@
         <v>7</v>
       </c>
       <c r="B109" t="s">
-        <v>315</v>
+        <v>1250</v>
       </c>
       <c r="D109" t="s">
-        <v>316</v>
+        <v>1251</v>
       </c>
       <c r="E109" t="s">
-        <v>948</v>
+        <v>1252</v>
       </c>
       <c r="F109" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G109" t="s">
         <v>11</v>
@@ -6338,13 +6422,13 @@
         <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>317</v>
+        <v>214</v>
       </c>
       <c r="D110" t="s">
-        <v>318</v>
+        <v>215</v>
       </c>
       <c r="E110" t="s">
-        <v>949</v>
+        <v>906</v>
       </c>
       <c r="F110" t="s">
         <v>10</v>
@@ -6358,13 +6442,13 @@
         <v>7</v>
       </c>
       <c r="B111" t="s">
-        <v>319</v>
+        <v>216</v>
       </c>
       <c r="D111" t="s">
-        <v>320</v>
+        <v>217</v>
       </c>
       <c r="E111" t="s">
-        <v>950</v>
+        <v>907</v>
       </c>
       <c r="F111" t="s">
         <v>10</v>
@@ -6375,16 +6459,16 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>321</v>
+        <v>218</v>
       </c>
       <c r="D112" t="s">
-        <v>322</v>
+        <v>219</v>
       </c>
       <c r="E112" t="s">
-        <v>951</v>
+        <v>908</v>
       </c>
       <c r="F112" t="s">
         <v>10</v>
@@ -6398,13 +6482,13 @@
         <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>323</v>
+        <v>220</v>
       </c>
       <c r="D113" t="s">
-        <v>324</v>
+        <v>221</v>
       </c>
       <c r="E113" t="s">
-        <v>952</v>
+        <v>909</v>
       </c>
       <c r="F113" t="s">
         <v>10</v>
@@ -6418,16 +6502,16 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>325</v>
+        <v>1253</v>
       </c>
       <c r="D114" t="s">
-        <v>326</v>
+        <v>1254</v>
       </c>
       <c r="E114" t="s">
-        <v>953</v>
+        <v>1255</v>
       </c>
       <c r="F114" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G114" t="s">
         <v>11</v>
@@ -6435,16 +6519,16 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B115" t="s">
-        <v>327</v>
+        <v>222</v>
       </c>
       <c r="D115" t="s">
-        <v>328</v>
+        <v>223</v>
       </c>
       <c r="E115" t="s">
-        <v>954</v>
+        <v>910</v>
       </c>
       <c r="F115" t="s">
         <v>10</v>
@@ -6458,16 +6542,19 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>329</v>
+        <v>224</v>
+      </c>
+      <c r="C116" t="s">
+        <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>330</v>
+        <v>225</v>
       </c>
       <c r="E116" t="s">
-        <v>955</v>
+        <v>1163</v>
       </c>
       <c r="F116" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G116" t="s">
         <v>11</v>
@@ -6478,16 +6565,19 @@
         <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>331</v>
+        <v>226</v>
+      </c>
+      <c r="C117" t="s">
+        <v>23</v>
       </c>
       <c r="D117" t="s">
-        <v>332</v>
+        <v>227</v>
       </c>
       <c r="E117" t="s">
-        <v>956</v>
+        <v>1164</v>
       </c>
       <c r="F117" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G117" t="s">
         <v>11</v>
@@ -6498,16 +6588,19 @@
         <v>7</v>
       </c>
       <c r="B118" t="s">
-        <v>333</v>
+        <v>228</v>
+      </c>
+      <c r="C118" t="s">
+        <v>23</v>
       </c>
       <c r="D118" t="s">
-        <v>334</v>
+        <v>229</v>
       </c>
       <c r="E118" t="s">
-        <v>957</v>
+        <v>1165</v>
       </c>
       <c r="F118" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G118" t="s">
         <v>11</v>
@@ -6515,16 +6608,16 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B119" t="s">
-        <v>335</v>
+        <v>230</v>
       </c>
       <c r="D119" t="s">
-        <v>336</v>
+        <v>231</v>
       </c>
       <c r="E119" t="s">
-        <v>958</v>
+        <v>911</v>
       </c>
       <c r="F119" t="s">
         <v>10</v>
@@ -6535,16 +6628,16 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>341</v>
+        <v>232</v>
       </c>
       <c r="D120" t="s">
-        <v>342</v>
+        <v>233</v>
       </c>
       <c r="E120" t="s">
-        <v>959</v>
+        <v>912</v>
       </c>
       <c r="F120" t="s">
         <v>10</v>
@@ -6558,13 +6651,13 @@
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>343</v>
+        <v>234</v>
       </c>
       <c r="D121" t="s">
-        <v>344</v>
+        <v>235</v>
       </c>
       <c r="E121" t="s">
-        <v>960</v>
+        <v>913</v>
       </c>
       <c r="F121" t="s">
         <v>10</v>
@@ -6578,13 +6671,13 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>345</v>
+        <v>236</v>
       </c>
       <c r="D122" t="s">
-        <v>346</v>
+        <v>237</v>
       </c>
       <c r="E122" t="s">
-        <v>961</v>
+        <v>914</v>
       </c>
       <c r="F122" t="s">
         <v>10</v>
@@ -6598,16 +6691,16 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>351</v>
+        <v>238</v>
       </c>
       <c r="D123" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E123" t="s">
-        <v>962</v>
+        <v>1166</v>
       </c>
       <c r="F123" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G123" t="s">
         <v>11</v>
@@ -6618,13 +6711,13 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>353</v>
+        <v>240</v>
       </c>
       <c r="D124" t="s">
-        <v>354</v>
+        <v>241</v>
       </c>
       <c r="E124" t="s">
-        <v>963</v>
+        <v>915</v>
       </c>
       <c r="F124" t="s">
         <v>10</v>
@@ -6638,13 +6731,13 @@
         <v>48</v>
       </c>
       <c r="B125" t="s">
-        <v>355</v>
+        <v>242</v>
       </c>
       <c r="D125" t="s">
-        <v>356</v>
+        <v>243</v>
       </c>
       <c r="E125" t="s">
-        <v>964</v>
+        <v>916</v>
       </c>
       <c r="F125" t="s">
         <v>10</v>
@@ -6658,13 +6751,13 @@
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>357</v>
+        <v>244</v>
       </c>
       <c r="D126" t="s">
-        <v>358</v>
+        <v>245</v>
       </c>
       <c r="E126" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="F126" t="s">
         <v>10</v>
@@ -6678,13 +6771,13 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>361</v>
+        <v>246</v>
       </c>
       <c r="D127" t="s">
-        <v>362</v>
+        <v>247</v>
       </c>
       <c r="E127" t="s">
-        <v>966</v>
+        <v>918</v>
       </c>
       <c r="F127" t="s">
         <v>10</v>
@@ -6695,19 +6788,19 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B128" t="s">
-        <v>363</v>
+        <v>248</v>
       </c>
       <c r="D128" t="s">
-        <v>364</v>
+        <v>249</v>
       </c>
       <c r="E128" t="s">
-        <v>967</v>
+        <v>1167</v>
       </c>
       <c r="F128" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G128" t="s">
         <v>11</v>
@@ -6715,16 +6808,16 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>365</v>
+        <v>250</v>
       </c>
       <c r="D129" t="s">
-        <v>366</v>
+        <v>251</v>
       </c>
       <c r="E129" t="s">
-        <v>968</v>
+        <v>919</v>
       </c>
       <c r="F129" t="s">
         <v>10</v>
@@ -6735,16 +6828,16 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="B130" t="s">
-        <v>367</v>
+        <v>252</v>
       </c>
       <c r="D130" t="s">
-        <v>368</v>
+        <v>253</v>
       </c>
       <c r="E130" t="s">
-        <v>969</v>
+        <v>920</v>
       </c>
       <c r="F130" t="s">
         <v>10</v>
@@ -6758,13 +6851,13 @@
         <v>7</v>
       </c>
       <c r="B131" t="s">
-        <v>369</v>
+        <v>254</v>
       </c>
       <c r="D131" t="s">
-        <v>370</v>
+        <v>255</v>
       </c>
       <c r="E131" t="s">
-        <v>970</v>
+        <v>921</v>
       </c>
       <c r="F131" t="s">
         <v>10</v>
@@ -6778,16 +6871,19 @@
         <v>7</v>
       </c>
       <c r="B132" t="s">
-        <v>375</v>
+        <v>256</v>
+      </c>
+      <c r="C132" t="s">
+        <v>23</v>
       </c>
       <c r="D132" t="s">
-        <v>376</v>
+        <v>257</v>
       </c>
       <c r="E132" t="s">
-        <v>971</v>
+        <v>1168</v>
       </c>
       <c r="F132" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G132" t="s">
         <v>11</v>
@@ -6795,19 +6891,19 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B133" t="s">
-        <v>377</v>
+        <v>258</v>
       </c>
       <c r="D133" t="s">
-        <v>378</v>
+        <v>259</v>
       </c>
       <c r="E133" t="s">
-        <v>972</v>
+        <v>1169</v>
       </c>
       <c r="F133" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G133" t="s">
         <v>11</v>
@@ -6818,13 +6914,13 @@
         <v>48</v>
       </c>
       <c r="B134" t="s">
-        <v>381</v>
+        <v>260</v>
       </c>
       <c r="D134" t="s">
-        <v>382</v>
+        <v>261</v>
       </c>
       <c r="E134" t="s">
-        <v>973</v>
+        <v>922</v>
       </c>
       <c r="F134" t="s">
         <v>10</v>
@@ -6835,19 +6931,19 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B135" t="s">
-        <v>383</v>
+        <v>262</v>
       </c>
       <c r="D135" t="s">
-        <v>384</v>
+        <v>263</v>
       </c>
       <c r="E135" t="s">
-        <v>974</v>
+        <v>1170</v>
       </c>
       <c r="F135" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G135" t="s">
         <v>11</v>
@@ -6858,16 +6954,16 @@
         <v>7</v>
       </c>
       <c r="B136" t="s">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="D136" t="s">
-        <v>386</v>
+        <v>265</v>
       </c>
       <c r="E136" t="s">
-        <v>975</v>
+        <v>1171</v>
       </c>
       <c r="F136" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G136" t="s">
         <v>11</v>
@@ -6878,13 +6974,13 @@
         <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>389</v>
+        <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>390</v>
+        <v>267</v>
       </c>
       <c r="E137" t="s">
-        <v>976</v>
+        <v>923</v>
       </c>
       <c r="F137" t="s">
         <v>10</v>
@@ -6898,13 +6994,13 @@
         <v>7</v>
       </c>
       <c r="B138" t="s">
-        <v>828</v>
+        <v>268</v>
       </c>
       <c r="D138" t="s">
-        <v>829</v>
+        <v>269</v>
       </c>
       <c r="E138" t="s">
-        <v>977</v>
+        <v>924</v>
       </c>
       <c r="F138" t="s">
         <v>10</v>
@@ -6918,16 +7014,16 @@
         <v>7</v>
       </c>
       <c r="B139" t="s">
-        <v>391</v>
+        <v>270</v>
       </c>
       <c r="D139" t="s">
-        <v>392</v>
+        <v>271</v>
       </c>
       <c r="E139" t="s">
-        <v>978</v>
+        <v>1172</v>
       </c>
       <c r="F139" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G139" t="s">
         <v>11</v>
@@ -6938,13 +7034,13 @@
         <v>7</v>
       </c>
       <c r="B140" t="s">
-        <v>393</v>
+        <v>272</v>
       </c>
       <c r="D140" t="s">
-        <v>394</v>
+        <v>273</v>
       </c>
       <c r="E140" t="s">
-        <v>979</v>
+        <v>925</v>
       </c>
       <c r="F140" t="s">
         <v>10</v>
@@ -6958,13 +7054,13 @@
         <v>7</v>
       </c>
       <c r="B141" t="s">
-        <v>399</v>
+        <v>274</v>
       </c>
       <c r="D141" t="s">
-        <v>400</v>
+        <v>275</v>
       </c>
       <c r="E141" t="s">
-        <v>980</v>
+        <v>926</v>
       </c>
       <c r="F141" t="s">
         <v>10</v>
@@ -6975,16 +7071,16 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B142" t="s">
-        <v>401</v>
+        <v>276</v>
       </c>
       <c r="D142" t="s">
-        <v>402</v>
+        <v>277</v>
       </c>
       <c r="E142" t="s">
-        <v>981</v>
+        <v>927</v>
       </c>
       <c r="F142" t="s">
         <v>10</v>
@@ -6995,16 +7091,16 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B143" t="s">
-        <v>403</v>
+        <v>278</v>
       </c>
       <c r="D143" t="s">
-        <v>404</v>
+        <v>279</v>
       </c>
       <c r="E143" t="s">
-        <v>982</v>
+        <v>928</v>
       </c>
       <c r="F143" t="s">
         <v>10</v>
@@ -7018,13 +7114,13 @@
         <v>7</v>
       </c>
       <c r="B144" t="s">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>281</v>
       </c>
       <c r="E144" t="s">
-        <v>983</v>
+        <v>929</v>
       </c>
       <c r="F144" t="s">
         <v>10</v>
@@ -7038,13 +7134,13 @@
         <v>7</v>
       </c>
       <c r="B145" t="s">
-        <v>407</v>
+        <v>282</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>283</v>
       </c>
       <c r="E145" t="s">
-        <v>984</v>
+        <v>930</v>
       </c>
       <c r="F145" t="s">
         <v>10</v>
@@ -7058,13 +7154,13 @@
         <v>48</v>
       </c>
       <c r="B146" t="s">
-        <v>409</v>
+        <v>284</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>285</v>
       </c>
       <c r="E146" t="s">
-        <v>985</v>
+        <v>931</v>
       </c>
       <c r="F146" t="s">
         <v>10</v>
@@ -7078,13 +7174,13 @@
         <v>7</v>
       </c>
       <c r="B147" t="s">
-        <v>411</v>
+        <v>286</v>
       </c>
       <c r="D147" t="s">
-        <v>412</v>
+        <v>287</v>
       </c>
       <c r="E147" t="s">
-        <v>986</v>
+        <v>932</v>
       </c>
       <c r="F147" t="s">
         <v>10</v>
@@ -7095,16 +7191,16 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>308</v>
+        <v>7</v>
       </c>
       <c r="B148" t="s">
-        <v>413</v>
+        <v>288</v>
       </c>
       <c r="D148" t="s">
-        <v>414</v>
+        <v>289</v>
       </c>
       <c r="E148" t="s">
-        <v>987</v>
+        <v>933</v>
       </c>
       <c r="F148" t="s">
         <v>10</v>
@@ -7115,16 +7211,16 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B149" t="s">
-        <v>415</v>
+        <v>290</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>291</v>
       </c>
       <c r="E149" t="s">
-        <v>988</v>
+        <v>934</v>
       </c>
       <c r="F149" t="s">
         <v>10</v>
@@ -7135,16 +7231,16 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B150" t="s">
-        <v>419</v>
+        <v>292</v>
       </c>
       <c r="D150" t="s">
-        <v>420</v>
+        <v>293</v>
       </c>
       <c r="E150" t="s">
-        <v>989</v>
+        <v>935</v>
       </c>
       <c r="F150" t="s">
         <v>10</v>
@@ -7158,13 +7254,13 @@
         <v>7</v>
       </c>
       <c r="B151" t="s">
-        <v>421</v>
+        <v>294</v>
       </c>
       <c r="D151" t="s">
-        <v>422</v>
+        <v>295</v>
       </c>
       <c r="E151" t="s">
-        <v>990</v>
+        <v>936</v>
       </c>
       <c r="F151" t="s">
         <v>10</v>
@@ -7175,16 +7271,16 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B152" t="s">
-        <v>423</v>
+        <v>296</v>
       </c>
       <c r="D152" t="s">
-        <v>424</v>
+        <v>297</v>
       </c>
       <c r="E152" t="s">
-        <v>991</v>
+        <v>937</v>
       </c>
       <c r="F152" t="s">
         <v>10</v>
@@ -7195,16 +7291,16 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B153" t="s">
-        <v>431</v>
+        <v>298</v>
       </c>
       <c r="D153" t="s">
-        <v>432</v>
+        <v>299</v>
       </c>
       <c r="E153" t="s">
-        <v>992</v>
+        <v>938</v>
       </c>
       <c r="F153" t="s">
         <v>10</v>
@@ -7218,13 +7314,13 @@
         <v>7</v>
       </c>
       <c r="B154" t="s">
-        <v>433</v>
+        <v>300</v>
       </c>
       <c r="D154" t="s">
-        <v>434</v>
+        <v>301</v>
       </c>
       <c r="E154" t="s">
-        <v>993</v>
+        <v>939</v>
       </c>
       <c r="F154" t="s">
         <v>10</v>
@@ -7235,16 +7331,16 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B155" t="s">
-        <v>435</v>
+        <v>302</v>
       </c>
       <c r="D155" t="s">
-        <v>436</v>
+        <v>303</v>
       </c>
       <c r="E155" t="s">
-        <v>994</v>
+        <v>940</v>
       </c>
       <c r="F155" t="s">
         <v>10</v>
@@ -7258,13 +7354,13 @@
         <v>7</v>
       </c>
       <c r="B156" t="s">
-        <v>437</v>
+        <v>304</v>
       </c>
       <c r="D156" t="s">
-        <v>438</v>
+        <v>305</v>
       </c>
       <c r="E156" t="s">
-        <v>995</v>
+        <v>941</v>
       </c>
       <c r="F156" t="s">
         <v>10</v>
@@ -7278,13 +7374,13 @@
         <v>7</v>
       </c>
       <c r="B157" t="s">
-        <v>439</v>
+        <v>306</v>
       </c>
       <c r="D157" t="s">
-        <v>440</v>
+        <v>307</v>
       </c>
       <c r="E157" t="s">
-        <v>996</v>
+        <v>942</v>
       </c>
       <c r="F157" t="s">
         <v>10</v>
@@ -7295,16 +7391,16 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>7</v>
+        <v>308</v>
       </c>
       <c r="B158" t="s">
-        <v>441</v>
+        <v>309</v>
       </c>
       <c r="D158" t="s">
-        <v>442</v>
+        <v>310</v>
       </c>
       <c r="E158" t="s">
-        <v>997</v>
+        <v>943</v>
       </c>
       <c r="F158" t="s">
         <v>10</v>
@@ -7315,16 +7411,16 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B159" t="s">
-        <v>443</v>
+        <v>311</v>
       </c>
       <c r="D159" t="s">
-        <v>444</v>
+        <v>312</v>
       </c>
       <c r="E159" t="s">
-        <v>998</v>
+        <v>944</v>
       </c>
       <c r="F159" t="s">
         <v>10</v>
@@ -7335,16 +7431,16 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B160" t="s">
-        <v>445</v>
+        <v>313</v>
       </c>
       <c r="D160" t="s">
-        <v>446</v>
+        <v>314</v>
       </c>
       <c r="E160" t="s">
-        <v>999</v>
+        <v>945</v>
       </c>
       <c r="F160" t="s">
         <v>10</v>
@@ -7358,13 +7454,13 @@
         <v>7</v>
       </c>
       <c r="B161" t="s">
-        <v>449</v>
+        <v>315</v>
       </c>
       <c r="D161" t="s">
-        <v>450</v>
+        <v>316</v>
       </c>
       <c r="E161" t="s">
-        <v>1000</v>
+        <v>946</v>
       </c>
       <c r="F161" t="s">
         <v>10</v>
@@ -7375,16 +7471,16 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B162" t="s">
-        <v>453</v>
+        <v>317</v>
       </c>
       <c r="D162" t="s">
-        <v>454</v>
+        <v>318</v>
       </c>
       <c r="E162" t="s">
-        <v>1001</v>
+        <v>947</v>
       </c>
       <c r="F162" t="s">
         <v>10</v>
@@ -7398,13 +7494,13 @@
         <v>7</v>
       </c>
       <c r="B163" t="s">
-        <v>455</v>
+        <v>319</v>
       </c>
       <c r="D163" t="s">
-        <v>456</v>
+        <v>320</v>
       </c>
       <c r="E163" t="s">
-        <v>1002</v>
+        <v>948</v>
       </c>
       <c r="F163" t="s">
         <v>10</v>
@@ -7415,16 +7511,16 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B164" t="s">
-        <v>457</v>
+        <v>321</v>
       </c>
       <c r="D164" t="s">
-        <v>458</v>
+        <v>322</v>
       </c>
       <c r="E164" t="s">
-        <v>1003</v>
+        <v>949</v>
       </c>
       <c r="F164" t="s">
         <v>10</v>
@@ -7438,13 +7534,13 @@
         <v>7</v>
       </c>
       <c r="B165" t="s">
-        <v>459</v>
+        <v>323</v>
       </c>
       <c r="D165" t="s">
-        <v>460</v>
+        <v>324</v>
       </c>
       <c r="E165" t="s">
-        <v>1004</v>
+        <v>950</v>
       </c>
       <c r="F165" t="s">
         <v>10</v>
@@ -7455,16 +7551,16 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="B166" t="s">
-        <v>461</v>
+        <v>325</v>
       </c>
       <c r="D166" t="s">
-        <v>462</v>
+        <v>326</v>
       </c>
       <c r="E166" t="s">
-        <v>1005</v>
+        <v>951</v>
       </c>
       <c r="F166" t="s">
         <v>10</v>
@@ -7475,16 +7571,16 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B167" t="s">
-        <v>463</v>
+        <v>327</v>
       </c>
       <c r="D167" t="s">
-        <v>464</v>
+        <v>328</v>
       </c>
       <c r="E167" t="s">
-        <v>1006</v>
+        <v>952</v>
       </c>
       <c r="F167" t="s">
         <v>10</v>
@@ -7495,16 +7591,16 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B168" t="s">
-        <v>465</v>
+        <v>329</v>
       </c>
       <c r="D168" t="s">
-        <v>466</v>
+        <v>330</v>
       </c>
       <c r="E168" t="s">
-        <v>1007</v>
+        <v>953</v>
       </c>
       <c r="F168" t="s">
         <v>10</v>
@@ -7515,16 +7611,16 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B169" t="s">
-        <v>467</v>
+        <v>331</v>
       </c>
       <c r="D169" t="s">
-        <v>468</v>
+        <v>332</v>
       </c>
       <c r="E169" t="s">
-        <v>1008</v>
+        <v>954</v>
       </c>
       <c r="F169" t="s">
         <v>10</v>
@@ -7535,16 +7631,16 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B170" t="s">
-        <v>469</v>
+        <v>333</v>
       </c>
       <c r="D170" t="s">
-        <v>470</v>
+        <v>334</v>
       </c>
       <c r="E170" t="s">
-        <v>1009</v>
+        <v>955</v>
       </c>
       <c r="F170" t="s">
         <v>10</v>
@@ -7558,13 +7654,13 @@
         <v>7</v>
       </c>
       <c r="B171" t="s">
-        <v>473</v>
+        <v>335</v>
       </c>
       <c r="D171" t="s">
-        <v>474</v>
+        <v>336</v>
       </c>
       <c r="E171" t="s">
-        <v>1010</v>
+        <v>956</v>
       </c>
       <c r="F171" t="s">
         <v>10</v>
@@ -7578,16 +7674,16 @@
         <v>7</v>
       </c>
       <c r="B172" t="s">
-        <v>475</v>
+        <v>337</v>
       </c>
       <c r="D172" t="s">
-        <v>476</v>
+        <v>338</v>
       </c>
       <c r="E172" t="s">
-        <v>1011</v>
+        <v>1173</v>
       </c>
       <c r="F172" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G172" t="s">
         <v>11</v>
@@ -7595,19 +7691,19 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B173" t="s">
-        <v>477</v>
+        <v>339</v>
       </c>
       <c r="D173" t="s">
-        <v>478</v>
+        <v>340</v>
       </c>
       <c r="E173" t="s">
-        <v>1012</v>
+        <v>1174</v>
       </c>
       <c r="F173" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G173" t="s">
         <v>11</v>
@@ -7615,16 +7711,16 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>479</v>
+        <v>341</v>
       </c>
       <c r="D174" t="s">
-        <v>480</v>
+        <v>342</v>
       </c>
       <c r="E174" t="s">
-        <v>1013</v>
+        <v>957</v>
       </c>
       <c r="F174" t="s">
         <v>10</v>
@@ -7638,13 +7734,13 @@
         <v>7</v>
       </c>
       <c r="B175" t="s">
-        <v>481</v>
+        <v>343</v>
       </c>
       <c r="D175" t="s">
-        <v>482</v>
+        <v>344</v>
       </c>
       <c r="E175" t="s">
-        <v>1014</v>
+        <v>958</v>
       </c>
       <c r="F175" t="s">
         <v>10</v>
@@ -7658,13 +7754,13 @@
         <v>7</v>
       </c>
       <c r="B176" t="s">
-        <v>485</v>
+        <v>345</v>
       </c>
       <c r="D176" t="s">
-        <v>486</v>
+        <v>346</v>
       </c>
       <c r="E176" t="s">
-        <v>1015</v>
+        <v>959</v>
       </c>
       <c r="F176" t="s">
         <v>10</v>
@@ -7675,19 +7771,19 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B177" t="s">
-        <v>487</v>
+        <v>347</v>
       </c>
       <c r="D177" t="s">
-        <v>488</v>
+        <v>348</v>
       </c>
       <c r="E177" t="s">
-        <v>1016</v>
+        <v>1175</v>
       </c>
       <c r="F177" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G177" t="s">
         <v>11</v>
@@ -7698,16 +7794,16 @@
         <v>7</v>
       </c>
       <c r="B178" t="s">
-        <v>489</v>
+        <v>349</v>
       </c>
       <c r="D178" t="s">
-        <v>490</v>
+        <v>350</v>
       </c>
       <c r="E178" t="s">
-        <v>1017</v>
+        <v>1176</v>
       </c>
       <c r="F178" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G178" t="s">
         <v>11</v>
@@ -7718,13 +7814,13 @@
         <v>7</v>
       </c>
       <c r="B179" t="s">
-        <v>491</v>
+        <v>351</v>
       </c>
       <c r="D179" t="s">
-        <v>492</v>
+        <v>352</v>
       </c>
       <c r="E179" t="s">
-        <v>1018</v>
+        <v>960</v>
       </c>
       <c r="F179" t="s">
         <v>10</v>
@@ -7738,13 +7834,13 @@
         <v>7</v>
       </c>
       <c r="B180" t="s">
-        <v>495</v>
+        <v>353</v>
       </c>
       <c r="D180" t="s">
-        <v>496</v>
+        <v>354</v>
       </c>
       <c r="E180" t="s">
-        <v>1019</v>
+        <v>961</v>
       </c>
       <c r="F180" t="s">
         <v>10</v>
@@ -7755,16 +7851,16 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B181" t="s">
-        <v>497</v>
+        <v>355</v>
       </c>
       <c r="D181" t="s">
-        <v>498</v>
+        <v>356</v>
       </c>
       <c r="E181" t="s">
-        <v>1020</v>
+        <v>962</v>
       </c>
       <c r="F181" t="s">
         <v>10</v>
@@ -7778,13 +7874,13 @@
         <v>7</v>
       </c>
       <c r="B182" t="s">
-        <v>499</v>
+        <v>357</v>
       </c>
       <c r="D182" t="s">
-        <v>500</v>
+        <v>358</v>
       </c>
       <c r="E182" t="s">
-        <v>1021</v>
+        <v>963</v>
       </c>
       <c r="F182" t="s">
         <v>10</v>
@@ -7795,19 +7891,22 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B183" t="s">
-        <v>501</v>
+        <v>359</v>
+      </c>
+      <c r="C183" t="s">
+        <v>23</v>
       </c>
       <c r="D183" t="s">
-        <v>502</v>
+        <v>360</v>
       </c>
       <c r="E183" t="s">
-        <v>1022</v>
+        <v>1177</v>
       </c>
       <c r="F183" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G183" t="s">
         <v>11</v>
@@ -7815,16 +7914,16 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B184" t="s">
-        <v>503</v>
+        <v>361</v>
       </c>
       <c r="D184" t="s">
-        <v>504</v>
+        <v>362</v>
       </c>
       <c r="E184" t="s">
-        <v>1019</v>
+        <v>964</v>
       </c>
       <c r="F184" t="s">
         <v>10</v>
@@ -7838,13 +7937,13 @@
         <v>7</v>
       </c>
       <c r="B185" t="s">
-        <v>505</v>
+        <v>363</v>
       </c>
       <c r="D185" t="s">
-        <v>506</v>
+        <v>364</v>
       </c>
       <c r="E185" t="s">
-        <v>1023</v>
+        <v>965</v>
       </c>
       <c r="F185" t="s">
         <v>10</v>
@@ -7855,16 +7954,16 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B186" t="s">
-        <v>507</v>
+        <v>365</v>
       </c>
       <c r="D186" t="s">
-        <v>508</v>
+        <v>366</v>
       </c>
       <c r="E186" t="s">
-        <v>1024</v>
+        <v>966</v>
       </c>
       <c r="F186" t="s">
         <v>10</v>
@@ -7878,13 +7977,13 @@
         <v>7</v>
       </c>
       <c r="B187" t="s">
-        <v>513</v>
+        <v>367</v>
       </c>
       <c r="D187" t="s">
-        <v>514</v>
+        <v>368</v>
       </c>
       <c r="E187" t="s">
-        <v>1025</v>
+        <v>967</v>
       </c>
       <c r="F187" t="s">
         <v>10</v>
@@ -7898,13 +7997,13 @@
         <v>7</v>
       </c>
       <c r="B188" t="s">
-        <v>517</v>
+        <v>369</v>
       </c>
       <c r="D188" t="s">
-        <v>518</v>
+        <v>370</v>
       </c>
       <c r="E188" t="s">
-        <v>1026</v>
+        <v>968</v>
       </c>
       <c r="F188" t="s">
         <v>10</v>
@@ -7915,19 +8014,19 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B189" t="s">
-        <v>519</v>
+        <v>1256</v>
       </c>
       <c r="D189" t="s">
-        <v>520</v>
+        <v>1257</v>
       </c>
       <c r="E189" t="s">
-        <v>1027</v>
+        <v>1258</v>
       </c>
       <c r="F189" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G189" t="s">
         <v>11</v>
@@ -7938,16 +8037,19 @@
         <v>7</v>
       </c>
       <c r="B190" t="s">
-        <v>521</v>
+        <v>371</v>
+      </c>
+      <c r="C190" t="s">
+        <v>23</v>
       </c>
       <c r="D190" t="s">
-        <v>522</v>
+        <v>372</v>
       </c>
       <c r="E190" t="s">
-        <v>1028</v>
+        <v>1175</v>
       </c>
       <c r="F190" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G190" t="s">
         <v>11</v>
@@ -7958,16 +8060,16 @@
         <v>7</v>
       </c>
       <c r="B191" t="s">
-        <v>531</v>
+        <v>373</v>
       </c>
       <c r="D191" t="s">
-        <v>532</v>
+        <v>374</v>
       </c>
       <c r="E191" t="s">
-        <v>1029</v>
+        <v>1178</v>
       </c>
       <c r="F191" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G191" t="s">
         <v>11</v>
@@ -7975,16 +8077,16 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B192" t="s">
-        <v>573</v>
+        <v>375</v>
       </c>
       <c r="D192" t="s">
-        <v>574</v>
+        <v>376</v>
       </c>
       <c r="E192" t="s">
-        <v>1030</v>
+        <v>969</v>
       </c>
       <c r="F192" t="s">
         <v>10</v>
@@ -7995,16 +8097,16 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="B193" t="s">
-        <v>575</v>
+        <v>377</v>
       </c>
       <c r="D193" t="s">
-        <v>576</v>
+        <v>378</v>
       </c>
       <c r="E193" t="s">
-        <v>1031</v>
+        <v>970</v>
       </c>
       <c r="F193" t="s">
         <v>10</v>
@@ -8018,16 +8120,16 @@
         <v>7</v>
       </c>
       <c r="B194" t="s">
-        <v>579</v>
+        <v>379</v>
       </c>
       <c r="D194" t="s">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="E194" t="s">
-        <v>1032</v>
+        <v>1179</v>
       </c>
       <c r="F194" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G194" t="s">
         <v>11</v>
@@ -8038,16 +8140,16 @@
         <v>7</v>
       </c>
       <c r="B195" t="s">
-        <v>581</v>
+        <v>822</v>
       </c>
       <c r="D195" t="s">
-        <v>582</v>
+        <v>823</v>
       </c>
       <c r="E195" t="s">
-        <v>1033</v>
+        <v>1180</v>
       </c>
       <c r="F195" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G195" t="s">
         <v>11</v>
@@ -8055,16 +8157,16 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="B196" t="s">
-        <v>583</v>
+        <v>381</v>
       </c>
       <c r="D196" t="s">
-        <v>584</v>
+        <v>382</v>
       </c>
       <c r="E196" t="s">
-        <v>1034</v>
+        <v>971</v>
       </c>
       <c r="F196" t="s">
         <v>10</v>
@@ -8075,16 +8177,16 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B197" t="s">
-        <v>585</v>
+        <v>383</v>
       </c>
       <c r="D197" t="s">
-        <v>586</v>
+        <v>384</v>
       </c>
       <c r="E197" t="s">
-        <v>1035</v>
+        <v>972</v>
       </c>
       <c r="F197" t="s">
         <v>10</v>
@@ -8098,13 +8200,13 @@
         <v>7</v>
       </c>
       <c r="B198" t="s">
-        <v>587</v>
+        <v>385</v>
       </c>
       <c r="D198" t="s">
-        <v>588</v>
+        <v>386</v>
       </c>
       <c r="E198" t="s">
-        <v>1036</v>
+        <v>973</v>
       </c>
       <c r="F198" t="s">
         <v>10</v>
@@ -8118,16 +8220,16 @@
         <v>7</v>
       </c>
       <c r="B199" t="s">
-        <v>591</v>
+        <v>824</v>
       </c>
       <c r="D199" t="s">
-        <v>592</v>
+        <v>825</v>
       </c>
       <c r="E199" t="s">
-        <v>983</v>
+        <v>1181</v>
       </c>
       <c r="F199" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G199" t="s">
         <v>11</v>
@@ -8135,19 +8237,19 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B200" t="s">
-        <v>593</v>
+        <v>387</v>
       </c>
       <c r="D200" t="s">
-        <v>594</v>
+        <v>388</v>
       </c>
       <c r="E200" t="s">
-        <v>1037</v>
+        <v>1182</v>
       </c>
       <c r="F200" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G200" t="s">
         <v>11</v>
@@ -8158,13 +8260,13 @@
         <v>7</v>
       </c>
       <c r="B201" t="s">
-        <v>595</v>
+        <v>389</v>
       </c>
       <c r="D201" t="s">
-        <v>596</v>
+        <v>390</v>
       </c>
       <c r="E201" t="s">
-        <v>1038</v>
+        <v>974</v>
       </c>
       <c r="F201" t="s">
         <v>10</v>
@@ -8178,13 +8280,13 @@
         <v>7</v>
       </c>
       <c r="B202" t="s">
-        <v>597</v>
+        <v>826</v>
       </c>
       <c r="D202" t="s">
-        <v>598</v>
+        <v>827</v>
       </c>
       <c r="E202" t="s">
-        <v>1039</v>
+        <v>975</v>
       </c>
       <c r="F202" t="s">
         <v>10</v>
@@ -8195,16 +8297,16 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="B203" t="s">
-        <v>599</v>
+        <v>391</v>
       </c>
       <c r="D203" t="s">
-        <v>600</v>
+        <v>392</v>
       </c>
       <c r="E203" t="s">
-        <v>1040</v>
+        <v>976</v>
       </c>
       <c r="F203" t="s">
         <v>10</v>
@@ -8215,16 +8317,16 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B204" t="s">
-        <v>601</v>
+        <v>393</v>
       </c>
       <c r="D204" t="s">
-        <v>602</v>
+        <v>394</v>
       </c>
       <c r="E204" t="s">
-        <v>1041</v>
+        <v>977</v>
       </c>
       <c r="F204" t="s">
         <v>10</v>
@@ -8238,16 +8340,16 @@
         <v>7</v>
       </c>
       <c r="B205" t="s">
-        <v>605</v>
+        <v>395</v>
       </c>
       <c r="D205" t="s">
-        <v>606</v>
+        <v>396</v>
       </c>
       <c r="E205" t="s">
-        <v>1042</v>
+        <v>1183</v>
       </c>
       <c r="F205" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G205" t="s">
         <v>11</v>
@@ -8258,16 +8360,16 @@
         <v>7</v>
       </c>
       <c r="B206" t="s">
-        <v>609</v>
+        <v>397</v>
       </c>
       <c r="D206" t="s">
-        <v>610</v>
+        <v>398</v>
       </c>
       <c r="E206" t="s">
-        <v>1043</v>
+        <v>1184</v>
       </c>
       <c r="F206" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G206" t="s">
         <v>11</v>
@@ -8278,13 +8380,13 @@
         <v>7</v>
       </c>
       <c r="B207" t="s">
-        <v>611</v>
+        <v>399</v>
       </c>
       <c r="D207" t="s">
-        <v>612</v>
+        <v>400</v>
       </c>
       <c r="E207" t="s">
-        <v>1044</v>
+        <v>978</v>
       </c>
       <c r="F207" t="s">
         <v>10</v>
@@ -8295,16 +8397,16 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B208" t="s">
-        <v>613</v>
+        <v>401</v>
       </c>
       <c r="D208" t="s">
-        <v>614</v>
+        <v>402</v>
       </c>
       <c r="E208" t="s">
-        <v>1045</v>
+        <v>979</v>
       </c>
       <c r="F208" t="s">
         <v>10</v>
@@ -8315,16 +8417,16 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B209" t="s">
-        <v>615</v>
+        <v>403</v>
       </c>
       <c r="D209" t="s">
-        <v>616</v>
+        <v>404</v>
       </c>
       <c r="E209" t="s">
-        <v>1046</v>
+        <v>980</v>
       </c>
       <c r="F209" t="s">
         <v>10</v>
@@ -8338,13 +8440,13 @@
         <v>7</v>
       </c>
       <c r="B210" t="s">
-        <v>617</v>
+        <v>405</v>
       </c>
       <c r="D210" t="s">
-        <v>618</v>
+        <v>406</v>
       </c>
       <c r="E210" t="s">
-        <v>1047</v>
+        <v>981</v>
       </c>
       <c r="F210" t="s">
         <v>10</v>
@@ -8355,16 +8457,16 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B211" t="s">
-        <v>619</v>
+        <v>407</v>
       </c>
       <c r="D211" t="s">
-        <v>620</v>
+        <v>408</v>
       </c>
       <c r="E211" t="s">
-        <v>1048</v>
+        <v>982</v>
       </c>
       <c r="F211" t="s">
         <v>10</v>
@@ -8375,16 +8477,16 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B212" t="s">
-        <v>621</v>
+        <v>409</v>
       </c>
       <c r="D212" t="s">
-        <v>622</v>
+        <v>410</v>
       </c>
       <c r="E212" t="s">
-        <v>1049</v>
+        <v>983</v>
       </c>
       <c r="F212" t="s">
         <v>10</v>
@@ -8398,13 +8500,13 @@
         <v>7</v>
       </c>
       <c r="B213" t="s">
-        <v>623</v>
+        <v>411</v>
       </c>
       <c r="D213" t="s">
-        <v>624</v>
+        <v>412</v>
       </c>
       <c r="E213" t="s">
-        <v>1050</v>
+        <v>984</v>
       </c>
       <c r="F213" t="s">
         <v>10</v>
@@ -8418,16 +8520,16 @@
         <v>7</v>
       </c>
       <c r="B214" t="s">
-        <v>625</v>
+        <v>828</v>
       </c>
       <c r="D214" t="s">
-        <v>626</v>
+        <v>829</v>
       </c>
       <c r="E214" t="s">
-        <v>1051</v>
+        <v>1185</v>
       </c>
       <c r="F214" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G214" t="s">
         <v>11</v>
@@ -8435,16 +8537,16 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>7</v>
+        <v>308</v>
       </c>
       <c r="B215" t="s">
-        <v>627</v>
+        <v>413</v>
       </c>
       <c r="D215" t="s">
-        <v>628</v>
+        <v>414</v>
       </c>
       <c r="E215" t="s">
-        <v>1052</v>
+        <v>985</v>
       </c>
       <c r="F215" t="s">
         <v>10</v>
@@ -8455,16 +8557,16 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>631</v>
+        <v>415</v>
       </c>
       <c r="D216" t="s">
-        <v>632</v>
+        <v>416</v>
       </c>
       <c r="E216" t="s">
-        <v>1053</v>
+        <v>986</v>
       </c>
       <c r="F216" t="s">
         <v>10</v>
@@ -8478,16 +8580,19 @@
         <v>7</v>
       </c>
       <c r="B217" t="s">
-        <v>633</v>
+        <v>417</v>
+      </c>
+      <c r="C217" t="s">
+        <v>23</v>
       </c>
       <c r="D217" t="s">
-        <v>634</v>
+        <v>418</v>
       </c>
       <c r="E217" t="s">
-        <v>1054</v>
+        <v>1186</v>
       </c>
       <c r="F217" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G217" t="s">
         <v>11</v>
@@ -8498,13 +8603,13 @@
         <v>7</v>
       </c>
       <c r="B218" t="s">
-        <v>635</v>
+        <v>419</v>
       </c>
       <c r="D218" t="s">
-        <v>636</v>
+        <v>420</v>
       </c>
       <c r="E218" t="s">
-        <v>1055</v>
+        <v>987</v>
       </c>
       <c r="F218" t="s">
         <v>10</v>
@@ -8518,13 +8623,13 @@
         <v>7</v>
       </c>
       <c r="B219" t="s">
-        <v>639</v>
+        <v>421</v>
       </c>
       <c r="D219" t="s">
-        <v>640</v>
+        <v>422</v>
       </c>
       <c r="E219" t="s">
-        <v>1056</v>
+        <v>988</v>
       </c>
       <c r="F219" t="s">
         <v>10</v>
@@ -8538,13 +8643,13 @@
         <v>7</v>
       </c>
       <c r="B220" t="s">
-        <v>641</v>
+        <v>423</v>
       </c>
       <c r="D220" t="s">
-        <v>642</v>
+        <v>424</v>
       </c>
       <c r="E220" t="s">
-        <v>1057</v>
+        <v>989</v>
       </c>
       <c r="F220" t="s">
         <v>10</v>
@@ -8555,19 +8660,19 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B221" t="s">
-        <v>645</v>
+        <v>425</v>
       </c>
       <c r="D221" t="s">
-        <v>646</v>
+        <v>426</v>
       </c>
       <c r="E221" t="s">
-        <v>1058</v>
+        <v>1187</v>
       </c>
       <c r="F221" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G221" t="s">
         <v>11</v>
@@ -8578,16 +8683,16 @@
         <v>7</v>
       </c>
       <c r="B222" t="s">
-        <v>647</v>
+        <v>427</v>
       </c>
       <c r="D222" t="s">
-        <v>648</v>
+        <v>428</v>
       </c>
       <c r="E222" t="s">
-        <v>1059</v>
+        <v>1188</v>
       </c>
       <c r="F222" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G222" t="s">
         <v>11</v>
@@ -8598,16 +8703,16 @@
         <v>7</v>
       </c>
       <c r="B223" t="s">
-        <v>649</v>
+        <v>429</v>
       </c>
       <c r="D223" t="s">
-        <v>650</v>
+        <v>430</v>
       </c>
       <c r="E223" t="s">
-        <v>1060</v>
+        <v>1189</v>
       </c>
       <c r="F223" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G223" t="s">
         <v>11</v>
@@ -8618,13 +8723,13 @@
         <v>7</v>
       </c>
       <c r="B224" t="s">
-        <v>651</v>
+        <v>431</v>
       </c>
       <c r="D224" t="s">
-        <v>652</v>
+        <v>432</v>
       </c>
       <c r="E224" t="s">
-        <v>1061</v>
+        <v>990</v>
       </c>
       <c r="F224" t="s">
         <v>10</v>
@@ -8638,13 +8743,13 @@
         <v>7</v>
       </c>
       <c r="B225" t="s">
-        <v>657</v>
+        <v>433</v>
       </c>
       <c r="D225" t="s">
-        <v>658</v>
+        <v>434</v>
       </c>
       <c r="E225" t="s">
-        <v>1062</v>
+        <v>991</v>
       </c>
       <c r="F225" t="s">
         <v>10</v>
@@ -8655,16 +8760,16 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>659</v>
+        <v>435</v>
       </c>
       <c r="D226" t="s">
-        <v>660</v>
+        <v>436</v>
       </c>
       <c r="E226" t="s">
-        <v>1063</v>
+        <v>992</v>
       </c>
       <c r="F226" t="s">
         <v>10</v>
@@ -8678,13 +8783,13 @@
         <v>7</v>
       </c>
       <c r="B227" t="s">
-        <v>663</v>
+        <v>437</v>
       </c>
       <c r="D227" t="s">
-        <v>664</v>
+        <v>438</v>
       </c>
       <c r="E227" t="s">
-        <v>1064</v>
+        <v>993</v>
       </c>
       <c r="F227" t="s">
         <v>10</v>
@@ -8695,16 +8800,16 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B228" t="s">
-        <v>665</v>
+        <v>439</v>
       </c>
       <c r="D228" t="s">
-        <v>666</v>
+        <v>440</v>
       </c>
       <c r="E228" t="s">
-        <v>1065</v>
+        <v>994</v>
       </c>
       <c r="F228" t="s">
         <v>10</v>
@@ -8715,16 +8820,16 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B229" t="s">
-        <v>667</v>
+        <v>441</v>
       </c>
       <c r="D229" t="s">
-        <v>668</v>
+        <v>442</v>
       </c>
       <c r="E229" t="s">
-        <v>1066</v>
+        <v>995</v>
       </c>
       <c r="F229" t="s">
         <v>10</v>
@@ -8738,13 +8843,13 @@
         <v>7</v>
       </c>
       <c r="B230" t="s">
-        <v>671</v>
+        <v>443</v>
       </c>
       <c r="D230" t="s">
-        <v>672</v>
+        <v>444</v>
       </c>
       <c r="E230" t="s">
-        <v>1067</v>
+        <v>996</v>
       </c>
       <c r="F230" t="s">
         <v>10</v>
@@ -8755,16 +8860,16 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B231" t="s">
-        <v>673</v>
+        <v>445</v>
       </c>
       <c r="D231" t="s">
-        <v>674</v>
+        <v>446</v>
       </c>
       <c r="E231" t="s">
-        <v>1068</v>
+        <v>997</v>
       </c>
       <c r="F231" t="s">
         <v>10</v>
@@ -8778,16 +8883,16 @@
         <v>7</v>
       </c>
       <c r="B232" t="s">
-        <v>675</v>
+        <v>447</v>
       </c>
       <c r="D232" t="s">
-        <v>676</v>
+        <v>448</v>
       </c>
       <c r="E232" t="s">
-        <v>1069</v>
+        <v>1190</v>
       </c>
       <c r="F232" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G232" t="s">
         <v>11</v>
@@ -8798,13 +8903,13 @@
         <v>7</v>
       </c>
       <c r="B233" t="s">
-        <v>677</v>
+        <v>449</v>
       </c>
       <c r="D233" t="s">
-        <v>678</v>
+        <v>450</v>
       </c>
       <c r="E233" t="s">
-        <v>1070</v>
+        <v>998</v>
       </c>
       <c r="F233" t="s">
         <v>10</v>
@@ -8815,19 +8920,19 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B234" t="s">
-        <v>679</v>
+        <v>451</v>
       </c>
       <c r="D234" t="s">
-        <v>680</v>
+        <v>452</v>
       </c>
       <c r="E234" t="s">
-        <v>1071</v>
+        <v>1191</v>
       </c>
       <c r="F234" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G234" t="s">
         <v>11</v>
@@ -8835,16 +8940,16 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B235" t="s">
-        <v>681</v>
+        <v>453</v>
       </c>
       <c r="D235" t="s">
-        <v>682</v>
+        <v>454</v>
       </c>
       <c r="E235" t="s">
-        <v>1072</v>
+        <v>999</v>
       </c>
       <c r="F235" t="s">
         <v>10</v>
@@ -8858,13 +8963,13 @@
         <v>7</v>
       </c>
       <c r="B236" t="s">
-        <v>683</v>
+        <v>455</v>
       </c>
       <c r="D236" t="s">
-        <v>684</v>
+        <v>456</v>
       </c>
       <c r="E236" t="s">
-        <v>1073</v>
+        <v>1000</v>
       </c>
       <c r="F236" t="s">
         <v>10</v>
@@ -8875,16 +8980,16 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B237" t="s">
-        <v>685</v>
+        <v>457</v>
       </c>
       <c r="D237" t="s">
-        <v>686</v>
+        <v>458</v>
       </c>
       <c r="E237" t="s">
-        <v>1074</v>
+        <v>1001</v>
       </c>
       <c r="F237" t="s">
         <v>10</v>
@@ -8898,13 +9003,13 @@
         <v>7</v>
       </c>
       <c r="B238" t="s">
-        <v>687</v>
+        <v>459</v>
       </c>
       <c r="D238" t="s">
-        <v>688</v>
+        <v>460</v>
       </c>
       <c r="E238" t="s">
-        <v>1075</v>
+        <v>1002</v>
       </c>
       <c r="F238" t="s">
         <v>10</v>
@@ -8915,16 +9020,16 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="B239" t="s">
-        <v>689</v>
+        <v>461</v>
       </c>
       <c r="D239" t="s">
-        <v>690</v>
+        <v>462</v>
       </c>
       <c r="E239" t="s">
-        <v>1076</v>
+        <v>1003</v>
       </c>
       <c r="F239" t="s">
         <v>10</v>
@@ -8935,16 +9040,16 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B240" t="s">
-        <v>691</v>
+        <v>463</v>
       </c>
       <c r="D240" t="s">
-        <v>692</v>
+        <v>464</v>
       </c>
       <c r="E240" t="s">
-        <v>1077</v>
+        <v>1004</v>
       </c>
       <c r="F240" t="s">
         <v>10</v>
@@ -8958,13 +9063,13 @@
         <v>48</v>
       </c>
       <c r="B241" t="s">
-        <v>693</v>
+        <v>465</v>
       </c>
       <c r="D241" t="s">
-        <v>694</v>
+        <v>466</v>
       </c>
       <c r="E241" t="s">
-        <v>1078</v>
+        <v>1005</v>
       </c>
       <c r="F241" t="s">
         <v>10</v>
@@ -8975,16 +9080,16 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B242" t="s">
-        <v>695</v>
+        <v>467</v>
       </c>
       <c r="D242" t="s">
-        <v>696</v>
+        <v>468</v>
       </c>
       <c r="E242" t="s">
-        <v>1079</v>
+        <v>1006</v>
       </c>
       <c r="F242" t="s">
         <v>10</v>
@@ -8995,16 +9100,16 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B243" t="s">
-        <v>697</v>
+        <v>469</v>
       </c>
       <c r="D243" t="s">
-        <v>698</v>
+        <v>470</v>
       </c>
       <c r="E243" t="s">
-        <v>1080</v>
+        <v>1007</v>
       </c>
       <c r="F243" t="s">
         <v>10</v>
@@ -9018,16 +9123,19 @@
         <v>7</v>
       </c>
       <c r="B244" t="s">
-        <v>699</v>
+        <v>471</v>
+      </c>
+      <c r="C244" t="s">
+        <v>23</v>
       </c>
       <c r="D244" t="s">
-        <v>700</v>
+        <v>472</v>
       </c>
       <c r="E244" t="s">
-        <v>1081</v>
+        <v>1192</v>
       </c>
       <c r="F244" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G244" t="s">
         <v>11</v>
@@ -9038,13 +9146,13 @@
         <v>7</v>
       </c>
       <c r="B245" t="s">
-        <v>701</v>
+        <v>473</v>
       </c>
       <c r="D245" t="s">
-        <v>702</v>
+        <v>474</v>
       </c>
       <c r="E245" t="s">
-        <v>1082</v>
+        <v>1008</v>
       </c>
       <c r="F245" t="s">
         <v>10</v>
@@ -9058,13 +9166,13 @@
         <v>7</v>
       </c>
       <c r="B246" t="s">
-        <v>703</v>
+        <v>475</v>
       </c>
       <c r="D246" t="s">
-        <v>704</v>
+        <v>476</v>
       </c>
       <c r="E246" t="s">
-        <v>1083</v>
+        <v>1009</v>
       </c>
       <c r="F246" t="s">
         <v>10</v>
@@ -9075,16 +9183,16 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>705</v>
+        <v>477</v>
       </c>
       <c r="D247" t="s">
-        <v>706</v>
+        <v>478</v>
       </c>
       <c r="E247" t="s">
-        <v>1084</v>
+        <v>1010</v>
       </c>
       <c r="F247" t="s">
         <v>10</v>
@@ -9098,13 +9206,13 @@
         <v>7</v>
       </c>
       <c r="B248" t="s">
-        <v>707</v>
+        <v>479</v>
       </c>
       <c r="D248" t="s">
-        <v>708</v>
+        <v>480</v>
       </c>
       <c r="E248" t="s">
-        <v>1085</v>
+        <v>1011</v>
       </c>
       <c r="F248" t="s">
         <v>10</v>
@@ -9115,16 +9223,16 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B249" t="s">
-        <v>709</v>
+        <v>481</v>
       </c>
       <c r="D249" t="s">
-        <v>710</v>
+        <v>482</v>
       </c>
       <c r="E249" t="s">
-        <v>1086</v>
+        <v>1012</v>
       </c>
       <c r="F249" t="s">
         <v>10</v>
@@ -9135,19 +9243,19 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B250" t="s">
-        <v>711</v>
+        <v>483</v>
       </c>
       <c r="D250" t="s">
-        <v>712</v>
+        <v>484</v>
       </c>
       <c r="E250" t="s">
-        <v>1087</v>
+        <v>1193</v>
       </c>
       <c r="F250" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G250" t="s">
         <v>11</v>
@@ -9158,16 +9266,16 @@
         <v>7</v>
       </c>
       <c r="B251" t="s">
-        <v>713</v>
+        <v>830</v>
       </c>
       <c r="D251" t="s">
-        <v>714</v>
+        <v>831</v>
       </c>
       <c r="E251" t="s">
-        <v>1088</v>
+        <v>1194</v>
       </c>
       <c r="F251" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G251" t="s">
         <v>11</v>
@@ -9175,16 +9283,16 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B252" t="s">
-        <v>715</v>
+        <v>485</v>
       </c>
       <c r="D252" t="s">
-        <v>716</v>
+        <v>486</v>
       </c>
       <c r="E252" t="s">
-        <v>1089</v>
+        <v>1013</v>
       </c>
       <c r="F252" t="s">
         <v>10</v>
@@ -9195,19 +9303,19 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B253" t="s">
-        <v>717</v>
+        <v>832</v>
       </c>
       <c r="D253" t="s">
-        <v>718</v>
+        <v>833</v>
       </c>
       <c r="E253" t="s">
-        <v>1090</v>
+        <v>1195</v>
       </c>
       <c r="F253" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G253" t="s">
         <v>11</v>
@@ -9215,16 +9323,16 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B254" t="s">
-        <v>721</v>
+        <v>487</v>
       </c>
       <c r="D254" t="s">
-        <v>722</v>
+        <v>488</v>
       </c>
       <c r="E254" t="s">
-        <v>1091</v>
+        <v>1014</v>
       </c>
       <c r="F254" t="s">
         <v>10</v>
@@ -9238,13 +9346,13 @@
         <v>7</v>
       </c>
       <c r="B255" t="s">
-        <v>725</v>
+        <v>489</v>
       </c>
       <c r="D255" t="s">
-        <v>726</v>
+        <v>490</v>
       </c>
       <c r="E255" t="s">
-        <v>1092</v>
+        <v>1015</v>
       </c>
       <c r="F255" t="s">
         <v>10</v>
@@ -9258,13 +9366,13 @@
         <v>7</v>
       </c>
       <c r="B256" t="s">
-        <v>727</v>
+        <v>491</v>
       </c>
       <c r="D256" t="s">
-        <v>728</v>
+        <v>492</v>
       </c>
       <c r="E256" t="s">
-        <v>1093</v>
+        <v>1016</v>
       </c>
       <c r="F256" t="s">
         <v>10</v>
@@ -9278,16 +9386,16 @@
         <v>7</v>
       </c>
       <c r="B257" t="s">
-        <v>729</v>
+        <v>493</v>
       </c>
       <c r="D257" t="s">
-        <v>730</v>
+        <v>494</v>
       </c>
       <c r="E257" t="s">
-        <v>1094</v>
+        <v>1196</v>
       </c>
       <c r="F257" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G257" t="s">
         <v>11</v>
@@ -9298,13 +9406,13 @@
         <v>7</v>
       </c>
       <c r="B258" t="s">
-        <v>731</v>
+        <v>495</v>
       </c>
       <c r="D258" t="s">
-        <v>732</v>
+        <v>496</v>
       </c>
       <c r="E258" t="s">
-        <v>1095</v>
+        <v>1017</v>
       </c>
       <c r="F258" t="s">
         <v>10</v>
@@ -9315,16 +9423,16 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B259" t="s">
-        <v>733</v>
+        <v>497</v>
       </c>
       <c r="D259" t="s">
-        <v>734</v>
+        <v>498</v>
       </c>
       <c r="E259" t="s">
-        <v>1096</v>
+        <v>1018</v>
       </c>
       <c r="F259" t="s">
         <v>10</v>
@@ -9338,13 +9446,13 @@
         <v>7</v>
       </c>
       <c r="B260" t="s">
-        <v>735</v>
+        <v>499</v>
       </c>
       <c r="D260" t="s">
-        <v>736</v>
+        <v>500</v>
       </c>
       <c r="E260" t="s">
-        <v>1097</v>
+        <v>1019</v>
       </c>
       <c r="F260" t="s">
         <v>10</v>
@@ -9355,16 +9463,16 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B261" t="s">
-        <v>737</v>
+        <v>501</v>
       </c>
       <c r="D261" t="s">
-        <v>738</v>
+        <v>502</v>
       </c>
       <c r="E261" t="s">
-        <v>1098</v>
+        <v>1020</v>
       </c>
       <c r="F261" t="s">
         <v>10</v>
@@ -9375,16 +9483,16 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B262" t="s">
-        <v>739</v>
+        <v>503</v>
       </c>
       <c r="D262" t="s">
-        <v>740</v>
+        <v>504</v>
       </c>
       <c r="E262" t="s">
-        <v>1099</v>
+        <v>1017</v>
       </c>
       <c r="F262" t="s">
         <v>10</v>
@@ -9395,16 +9503,16 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B263" t="s">
-        <v>741</v>
+        <v>505</v>
       </c>
       <c r="D263" t="s">
-        <v>742</v>
+        <v>506</v>
       </c>
       <c r="E263" t="s">
-        <v>1100</v>
+        <v>1021</v>
       </c>
       <c r="F263" t="s">
         <v>10</v>
@@ -9418,13 +9526,13 @@
         <v>7</v>
       </c>
       <c r="B264" t="s">
-        <v>743</v>
+        <v>507</v>
       </c>
       <c r="D264" t="s">
-        <v>744</v>
+        <v>508</v>
       </c>
       <c r="E264" t="s">
-        <v>1101</v>
+        <v>1022</v>
       </c>
       <c r="F264" t="s">
         <v>10</v>
@@ -9438,16 +9546,19 @@
         <v>7</v>
       </c>
       <c r="B265" t="s">
-        <v>745</v>
+        <v>509</v>
+      </c>
+      <c r="C265" t="s">
+        <v>23</v>
       </c>
       <c r="D265" t="s">
-        <v>746</v>
+        <v>510</v>
       </c>
       <c r="E265" t="s">
-        <v>1102</v>
+        <v>1197</v>
       </c>
       <c r="F265" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G265" t="s">
         <v>11</v>
@@ -9458,16 +9569,19 @@
         <v>7</v>
       </c>
       <c r="B266" t="s">
-        <v>749</v>
+        <v>511</v>
+      </c>
+      <c r="C266" t="s">
+        <v>23</v>
       </c>
       <c r="D266" t="s">
-        <v>750</v>
+        <v>512</v>
       </c>
       <c r="E266" t="s">
-        <v>1103</v>
+        <v>1198</v>
       </c>
       <c r="F266" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G266" t="s">
         <v>11</v>
@@ -9478,13 +9592,13 @@
         <v>7</v>
       </c>
       <c r="B267" t="s">
-        <v>751</v>
+        <v>513</v>
       </c>
       <c r="D267" t="s">
-        <v>752</v>
+        <v>514</v>
       </c>
       <c r="E267" t="s">
-        <v>1104</v>
+        <v>1023</v>
       </c>
       <c r="F267" t="s">
         <v>10</v>
@@ -9495,19 +9609,19 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B268" t="s">
-        <v>753</v>
+        <v>515</v>
       </c>
       <c r="D268" t="s">
-        <v>754</v>
+        <v>516</v>
       </c>
       <c r="E268" t="s">
-        <v>1105</v>
+        <v>1199</v>
       </c>
       <c r="F268" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G268" t="s">
         <v>11</v>
@@ -9518,13 +9632,13 @@
         <v>7</v>
       </c>
       <c r="B269" t="s">
-        <v>755</v>
+        <v>517</v>
       </c>
       <c r="D269" t="s">
-        <v>756</v>
+        <v>518</v>
       </c>
       <c r="E269" t="s">
-        <v>1106</v>
+        <v>1024</v>
       </c>
       <c r="F269" t="s">
         <v>10</v>
@@ -9535,16 +9649,16 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B270" t="s">
-        <v>757</v>
+        <v>519</v>
       </c>
       <c r="D270" t="s">
-        <v>758</v>
+        <v>520</v>
       </c>
       <c r="E270" t="s">
-        <v>1107</v>
+        <v>1025</v>
       </c>
       <c r="F270" t="s">
         <v>10</v>
@@ -9558,13 +9672,13 @@
         <v>7</v>
       </c>
       <c r="B271" t="s">
-        <v>759</v>
+        <v>521</v>
       </c>
       <c r="D271" t="s">
-        <v>760</v>
+        <v>522</v>
       </c>
       <c r="E271" t="s">
-        <v>1108</v>
+        <v>1026</v>
       </c>
       <c r="F271" t="s">
         <v>10</v>
@@ -9578,16 +9692,19 @@
         <v>7</v>
       </c>
       <c r="B272" t="s">
-        <v>761</v>
+        <v>523</v>
+      </c>
+      <c r="C272" t="s">
+        <v>23</v>
       </c>
       <c r="D272" t="s">
-        <v>762</v>
+        <v>524</v>
       </c>
       <c r="E272" t="s">
-        <v>1109</v>
+        <v>1200</v>
       </c>
       <c r="F272" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G272" t="s">
         <v>11</v>
@@ -9595,19 +9712,22 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B273" t="s">
-        <v>765</v>
+        <v>525</v>
+      </c>
+      <c r="C273" t="s">
+        <v>23</v>
       </c>
       <c r="D273" t="s">
-        <v>766</v>
+        <v>526</v>
       </c>
       <c r="E273" t="s">
-        <v>1110</v>
+        <v>1201</v>
       </c>
       <c r="F273" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G273" t="s">
         <v>11</v>
@@ -9615,19 +9735,22 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>770</v>
+        <v>7</v>
       </c>
       <c r="B274" t="s">
-        <v>771</v>
+        <v>527</v>
+      </c>
+      <c r="C274" t="s">
+        <v>23</v>
       </c>
       <c r="D274" t="s">
-        <v>772</v>
+        <v>528</v>
       </c>
       <c r="E274" t="s">
-        <v>1111</v>
+        <v>1202</v>
       </c>
       <c r="F274" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G274" t="s">
         <v>11</v>
@@ -9638,13 +9761,13 @@
         <v>7</v>
       </c>
       <c r="B275" t="s">
-        <v>774</v>
+        <v>529</v>
       </c>
       <c r="D275" t="s">
-        <v>775</v>
+        <v>530</v>
       </c>
       <c r="E275" t="s">
-        <v>1112</v>
+        <v>1027</v>
       </c>
       <c r="F275" t="s">
         <v>10</v>
@@ -9658,16 +9781,16 @@
         <v>7</v>
       </c>
       <c r="B276" t="s">
-        <v>776</v>
+        <v>834</v>
       </c>
       <c r="D276" t="s">
-        <v>777</v>
+        <v>835</v>
       </c>
       <c r="E276" t="s">
-        <v>1113</v>
+        <v>1203</v>
       </c>
       <c r="F276" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G276" t="s">
         <v>11</v>
@@ -9678,16 +9801,16 @@
         <v>7</v>
       </c>
       <c r="B277" t="s">
-        <v>778</v>
+        <v>531</v>
       </c>
       <c r="D277" t="s">
-        <v>779</v>
+        <v>532</v>
       </c>
       <c r="E277" t="s">
-        <v>1114</v>
+        <v>1204</v>
       </c>
       <c r="F277" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G277" t="s">
         <v>11</v>
@@ -9695,19 +9818,22 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B278" t="s">
-        <v>780</v>
+        <v>533</v>
+      </c>
+      <c r="C278" t="s">
+        <v>23</v>
       </c>
       <c r="D278" t="s">
-        <v>781</v>
+        <v>534</v>
       </c>
       <c r="E278" t="s">
-        <v>1115</v>
+        <v>1205</v>
       </c>
       <c r="F278" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G278" t="s">
         <v>11</v>
@@ -9718,16 +9844,19 @@
         <v>7</v>
       </c>
       <c r="B279" t="s">
-        <v>782</v>
+        <v>535</v>
+      </c>
+      <c r="C279" t="s">
+        <v>23</v>
       </c>
       <c r="D279" t="s">
-        <v>783</v>
+        <v>536</v>
       </c>
       <c r="E279" t="s">
-        <v>1116</v>
+        <v>1206</v>
       </c>
       <c r="F279" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G279" t="s">
         <v>11</v>
@@ -9735,19 +9864,22 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B280" t="s">
-        <v>784</v>
+        <v>537</v>
+      </c>
+      <c r="C280" t="s">
+        <v>23</v>
       </c>
       <c r="D280" t="s">
-        <v>785</v>
+        <v>538</v>
       </c>
       <c r="E280" t="s">
-        <v>1117</v>
+        <v>1207</v>
       </c>
       <c r="F280" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G280" t="s">
         <v>11</v>
@@ -9758,16 +9890,19 @@
         <v>7</v>
       </c>
       <c r="B281" t="s">
-        <v>786</v>
+        <v>539</v>
+      </c>
+      <c r="C281" t="s">
+        <v>23</v>
       </c>
       <c r="D281" t="s">
-        <v>787</v>
+        <v>540</v>
       </c>
       <c r="E281" t="s">
-        <v>1118</v>
+        <v>1208</v>
       </c>
       <c r="F281" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G281" t="s">
         <v>11</v>
@@ -9778,16 +9913,19 @@
         <v>7</v>
       </c>
       <c r="B282" t="s">
-        <v>791</v>
+        <v>541</v>
+      </c>
+      <c r="C282" t="s">
+        <v>23</v>
       </c>
       <c r="D282" t="s">
-        <v>792</v>
+        <v>542</v>
       </c>
       <c r="E282" t="s">
-        <v>1119</v>
+        <v>1209</v>
       </c>
       <c r="F282" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G282" t="s">
         <v>11</v>
@@ -9795,19 +9933,22 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B283" t="s">
-        <v>793</v>
+        <v>543</v>
+      </c>
+      <c r="C283" t="s">
+        <v>23</v>
       </c>
       <c r="D283" t="s">
-        <v>794</v>
+        <v>544</v>
       </c>
       <c r="E283" t="s">
-        <v>1120</v>
+        <v>1210</v>
       </c>
       <c r="F283" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G283" t="s">
         <v>11</v>
@@ -9815,19 +9956,22 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B284" t="s">
-        <v>795</v>
+        <v>545</v>
+      </c>
+      <c r="C284" t="s">
+        <v>23</v>
       </c>
       <c r="D284" t="s">
-        <v>796</v>
+        <v>546</v>
       </c>
       <c r="E284" t="s">
-        <v>1121</v>
+        <v>1211</v>
       </c>
       <c r="F284" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G284" t="s">
         <v>11</v>
@@ -9835,19 +9979,22 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B285" t="s">
-        <v>797</v>
+        <v>547</v>
+      </c>
+      <c r="C285" t="s">
+        <v>23</v>
       </c>
       <c r="D285" t="s">
-        <v>798</v>
+        <v>548</v>
       </c>
       <c r="E285" t="s">
-        <v>1122</v>
+        <v>1212</v>
       </c>
       <c r="F285" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G285" t="s">
         <v>11</v>
@@ -9855,19 +10002,22 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B286" t="s">
-        <v>799</v>
+        <v>549</v>
+      </c>
+      <c r="C286" t="s">
+        <v>23</v>
       </c>
       <c r="D286" t="s">
-        <v>800</v>
+        <v>550</v>
       </c>
       <c r="E286" t="s">
-        <v>1123</v>
+        <v>1213</v>
       </c>
       <c r="F286" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G286" t="s">
         <v>11</v>
@@ -9875,19 +10025,19 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B287" t="s">
-        <v>801</v>
+        <v>551</v>
       </c>
       <c r="D287" t="s">
-        <v>802</v>
+        <v>552</v>
       </c>
       <c r="E287" t="s">
-        <v>1124</v>
+        <v>1214</v>
       </c>
       <c r="F287" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G287" t="s">
         <v>11</v>
@@ -9898,16 +10048,19 @@
         <v>7</v>
       </c>
       <c r="B288" t="s">
-        <v>803</v>
+        <v>553</v>
+      </c>
+      <c r="C288" t="s">
+        <v>23</v>
       </c>
       <c r="D288" t="s">
-        <v>804</v>
+        <v>554</v>
       </c>
       <c r="E288" t="s">
-        <v>1125</v>
+        <v>1215</v>
       </c>
       <c r="F288" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G288" t="s">
         <v>11</v>
@@ -9915,19 +10068,22 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B289" t="s">
-        <v>805</v>
+        <v>555</v>
+      </c>
+      <c r="C289" t="s">
+        <v>23</v>
       </c>
       <c r="D289" t="s">
-        <v>806</v>
+        <v>556</v>
       </c>
       <c r="E289" t="s">
-        <v>1126</v>
+        <v>1216</v>
       </c>
       <c r="F289" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G289" t="s">
         <v>11</v>
@@ -9938,16 +10094,19 @@
         <v>7</v>
       </c>
       <c r="B290" t="s">
-        <v>807</v>
+        <v>557</v>
+      </c>
+      <c r="C290" t="s">
+        <v>23</v>
       </c>
       <c r="D290" t="s">
-        <v>808</v>
+        <v>558</v>
       </c>
       <c r="E290" t="s">
-        <v>1127</v>
+        <v>1217</v>
       </c>
       <c r="F290" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G290" t="s">
         <v>11</v>
@@ -9958,16 +10117,19 @@
         <v>7</v>
       </c>
       <c r="B291" t="s">
-        <v>809</v>
+        <v>559</v>
+      </c>
+      <c r="C291" t="s">
+        <v>23</v>
       </c>
       <c r="D291" t="s">
-        <v>810</v>
+        <v>560</v>
       </c>
       <c r="E291" t="s">
-        <v>1128</v>
+        <v>1218</v>
       </c>
       <c r="F291" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G291" t="s">
         <v>11</v>
@@ -9978,13 +10140,16 @@
         <v>7</v>
       </c>
       <c r="B292" t="s">
-        <v>15</v>
+        <v>561</v>
+      </c>
+      <c r="C292" t="s">
+        <v>23</v>
       </c>
       <c r="D292" t="s">
-        <v>16</v>
+        <v>562</v>
       </c>
       <c r="E292" t="s">
-        <v>1129</v>
+        <v>1219</v>
       </c>
       <c r="F292" t="s">
         <v>17</v>
@@ -9998,16 +10163,16 @@
         <v>7</v>
       </c>
       <c r="B293" t="s">
-        <v>22</v>
+        <v>563</v>
       </c>
       <c r="C293" t="s">
         <v>23</v>
       </c>
       <c r="D293" t="s">
-        <v>24</v>
+        <v>564</v>
       </c>
       <c r="E293" t="s">
-        <v>1130</v>
+        <v>1220</v>
       </c>
       <c r="F293" t="s">
         <v>17</v>
@@ -10021,13 +10186,16 @@
         <v>7</v>
       </c>
       <c r="B294" t="s">
-        <v>25</v>
+        <v>565</v>
+      </c>
+      <c r="C294" t="s">
+        <v>23</v>
       </c>
       <c r="D294" t="s">
-        <v>26</v>
+        <v>566</v>
       </c>
       <c r="E294" t="s">
-        <v>1131</v>
+        <v>1221</v>
       </c>
       <c r="F294" t="s">
         <v>17</v>
@@ -10041,16 +10209,16 @@
         <v>7</v>
       </c>
       <c r="B295" t="s">
-        <v>36</v>
+        <v>567</v>
       </c>
       <c r="C295" t="s">
         <v>23</v>
       </c>
       <c r="D295" t="s">
-        <v>37</v>
+        <v>568</v>
       </c>
       <c r="E295" t="s">
-        <v>1132</v>
+        <v>1222</v>
       </c>
       <c r="F295" t="s">
         <v>17</v>
@@ -10064,13 +10232,16 @@
         <v>7</v>
       </c>
       <c r="B296" t="s">
-        <v>38</v>
+        <v>569</v>
+      </c>
+      <c r="C296" t="s">
+        <v>23</v>
       </c>
       <c r="D296" t="s">
-        <v>39</v>
+        <v>570</v>
       </c>
       <c r="E296" t="s">
-        <v>1133</v>
+        <v>1223</v>
       </c>
       <c r="F296" t="s">
         <v>17</v>
@@ -10081,22 +10252,19 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B297" t="s">
-        <v>51</v>
-      </c>
-      <c r="C297" t="s">
-        <v>23</v>
+        <v>571</v>
       </c>
       <c r="D297" t="s">
-        <v>52</v>
+        <v>572</v>
       </c>
       <c r="E297" t="s">
-        <v>1134</v>
+        <v>1028</v>
       </c>
       <c r="F297" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G297" t="s">
         <v>11</v>
@@ -10104,19 +10272,19 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B298" t="s">
-        <v>69</v>
+        <v>573</v>
       </c>
       <c r="D298" t="s">
-        <v>70</v>
+        <v>574</v>
       </c>
       <c r="E298" t="s">
-        <v>1135</v>
+        <v>1029</v>
       </c>
       <c r="F298" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G298" t="s">
         <v>11</v>
@@ -10127,16 +10295,16 @@
         <v>7</v>
       </c>
       <c r="B299" t="s">
-        <v>811</v>
+        <v>575</v>
       </c>
       <c r="C299" t="s">
-        <v>812</v>
+        <v>23</v>
       </c>
       <c r="D299" t="s">
-        <v>813</v>
+        <v>576</v>
       </c>
       <c r="E299" t="s">
-        <v>1136</v>
+        <v>1224</v>
       </c>
       <c r="F299" t="s">
         <v>17</v>
@@ -10150,16 +10318,16 @@
         <v>7</v>
       </c>
       <c r="B300" t="s">
-        <v>90</v>
+        <v>577</v>
       </c>
       <c r="D300" t="s">
-        <v>91</v>
+        <v>578</v>
       </c>
       <c r="E300" t="s">
-        <v>1137</v>
+        <v>1030</v>
       </c>
       <c r="F300" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G300" t="s">
         <v>11</v>
@@ -10170,16 +10338,16 @@
         <v>7</v>
       </c>
       <c r="B301" t="s">
-        <v>96</v>
+        <v>579</v>
       </c>
       <c r="D301" t="s">
-        <v>97</v>
+        <v>580</v>
       </c>
       <c r="E301" t="s">
-        <v>1138</v>
+        <v>1031</v>
       </c>
       <c r="F301" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G301" t="s">
         <v>11</v>
@@ -10187,22 +10355,19 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B302" t="s">
-        <v>100</v>
-      </c>
-      <c r="C302" t="s">
-        <v>23</v>
+        <v>581</v>
       </c>
       <c r="D302" t="s">
-        <v>101</v>
+        <v>582</v>
       </c>
       <c r="E302" t="s">
-        <v>1139</v>
+        <v>1032</v>
       </c>
       <c r="F302" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G302" t="s">
         <v>11</v>
@@ -10213,16 +10378,16 @@
         <v>7</v>
       </c>
       <c r="B303" t="s">
-        <v>102</v>
+        <v>583</v>
       </c>
       <c r="D303" t="s">
-        <v>103</v>
+        <v>584</v>
       </c>
       <c r="E303" t="s">
-        <v>1140</v>
+        <v>1033</v>
       </c>
       <c r="F303" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G303" t="s">
         <v>11</v>
@@ -10233,16 +10398,16 @@
         <v>7</v>
       </c>
       <c r="B304" t="s">
-        <v>104</v>
+        <v>585</v>
       </c>
       <c r="D304" t="s">
-        <v>105</v>
+        <v>586</v>
       </c>
       <c r="E304" t="s">
-        <v>1141</v>
+        <v>1034</v>
       </c>
       <c r="F304" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G304" t="s">
         <v>11</v>
@@ -10250,16 +10415,19 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B305" t="s">
-        <v>108</v>
+        <v>587</v>
+      </c>
+      <c r="C305" t="s">
+        <v>23</v>
       </c>
       <c r="D305" t="s">
-        <v>109</v>
+        <v>588</v>
       </c>
       <c r="E305" t="s">
-        <v>1142</v>
+        <v>1225</v>
       </c>
       <c r="F305" t="s">
         <v>17</v>
@@ -10273,16 +10441,16 @@
         <v>7</v>
       </c>
       <c r="B306" t="s">
-        <v>110</v>
+        <v>589</v>
       </c>
       <c r="D306" t="s">
-        <v>111</v>
+        <v>590</v>
       </c>
       <c r="E306" t="s">
-        <v>1143</v>
+        <v>981</v>
       </c>
       <c r="F306" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G306" t="s">
         <v>11</v>
@@ -10293,16 +10461,16 @@
         <v>48</v>
       </c>
       <c r="B307" t="s">
-        <v>112</v>
+        <v>591</v>
       </c>
       <c r="D307" t="s">
-        <v>113</v>
+        <v>592</v>
       </c>
       <c r="E307" t="s">
-        <v>1144</v>
+        <v>1035</v>
       </c>
       <c r="F307" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G307" t="s">
         <v>11</v>
@@ -10313,16 +10481,16 @@
         <v>7</v>
       </c>
       <c r="B308" t="s">
-        <v>122</v>
+        <v>593</v>
       </c>
       <c r="D308" t="s">
-        <v>123</v>
+        <v>594</v>
       </c>
       <c r="E308" t="s">
-        <v>1145</v>
+        <v>1036</v>
       </c>
       <c r="F308" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G308" t="s">
         <v>11</v>
@@ -10333,19 +10501,16 @@
         <v>7</v>
       </c>
       <c r="B309" t="s">
-        <v>124</v>
-      </c>
-      <c r="C309" t="s">
-        <v>23</v>
+        <v>595</v>
       </c>
       <c r="D309" t="s">
-        <v>125</v>
+        <v>596</v>
       </c>
       <c r="E309" t="s">
-        <v>1146</v>
+        <v>1037</v>
       </c>
       <c r="F309" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G309" t="s">
         <v>11</v>
@@ -10353,22 +10518,19 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="B310" t="s">
-        <v>126</v>
-      </c>
-      <c r="C310" t="s">
-        <v>23</v>
+        <v>597</v>
       </c>
       <c r="D310" t="s">
-        <v>127</v>
+        <v>598</v>
       </c>
       <c r="E310" t="s">
-        <v>1147</v>
+        <v>1038</v>
       </c>
       <c r="F310" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G310" t="s">
         <v>11</v>
@@ -10376,22 +10538,19 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B311" t="s">
-        <v>130</v>
-      </c>
-      <c r="C311" t="s">
-        <v>23</v>
+        <v>599</v>
       </c>
       <c r="D311" t="s">
-        <v>131</v>
+        <v>600</v>
       </c>
       <c r="E311" t="s">
-        <v>1148</v>
+        <v>1039</v>
       </c>
       <c r="F311" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G311" t="s">
         <v>11</v>
@@ -10402,13 +10561,13 @@
         <v>7</v>
       </c>
       <c r="B312" t="s">
-        <v>814</v>
+        <v>601</v>
       </c>
       <c r="D312" t="s">
-        <v>815</v>
+        <v>602</v>
       </c>
       <c r="E312" t="s">
-        <v>1149</v>
+        <v>1226</v>
       </c>
       <c r="F312" t="s">
         <v>17</v>
@@ -10422,16 +10581,16 @@
         <v>7</v>
       </c>
       <c r="B313" t="s">
-        <v>134</v>
+        <v>603</v>
       </c>
       <c r="D313" t="s">
-        <v>135</v>
+        <v>604</v>
       </c>
       <c r="E313" t="s">
-        <v>1150</v>
+        <v>1040</v>
       </c>
       <c r="F313" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G313" t="s">
         <v>11</v>
@@ -10442,13 +10601,16 @@
         <v>7</v>
       </c>
       <c r="B314" t="s">
-        <v>816</v>
+        <v>605</v>
+      </c>
+      <c r="C314" t="s">
+        <v>23</v>
       </c>
       <c r="D314" t="s">
-        <v>817</v>
+        <v>606</v>
       </c>
       <c r="E314" t="s">
-        <v>1151</v>
+        <v>1227</v>
       </c>
       <c r="F314" t="s">
         <v>17</v>
@@ -10462,16 +10624,16 @@
         <v>7</v>
       </c>
       <c r="B315" t="s">
-        <v>136</v>
+        <v>607</v>
       </c>
       <c r="D315" t="s">
-        <v>137</v>
+        <v>608</v>
       </c>
       <c r="E315" t="s">
-        <v>1152</v>
+        <v>1041</v>
       </c>
       <c r="F315" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G315" t="s">
         <v>11</v>
@@ -10482,19 +10644,16 @@
         <v>7</v>
       </c>
       <c r="B316" t="s">
-        <v>138</v>
-      </c>
-      <c r="C316" t="s">
-        <v>23</v>
+        <v>609</v>
       </c>
       <c r="D316" t="s">
-        <v>139</v>
+        <v>610</v>
       </c>
       <c r="E316" t="s">
-        <v>1153</v>
+        <v>1042</v>
       </c>
       <c r="F316" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G316" t="s">
         <v>11</v>
@@ -10502,22 +10661,19 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B317" t="s">
-        <v>140</v>
-      </c>
-      <c r="C317" t="s">
-        <v>23</v>
+        <v>611</v>
       </c>
       <c r="D317" t="s">
-        <v>141</v>
+        <v>612</v>
       </c>
       <c r="E317" t="s">
-        <v>1143</v>
+        <v>1043</v>
       </c>
       <c r="F317" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G317" t="s">
         <v>11</v>
@@ -10528,19 +10684,16 @@
         <v>7</v>
       </c>
       <c r="B318" t="s">
-        <v>142</v>
-      </c>
-      <c r="C318" t="s">
-        <v>23</v>
+        <v>613</v>
       </c>
       <c r="D318" t="s">
-        <v>143</v>
+        <v>614</v>
       </c>
       <c r="E318" t="s">
-        <v>1154</v>
+        <v>1044</v>
       </c>
       <c r="F318" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G318" t="s">
         <v>11</v>
@@ -10551,19 +10704,16 @@
         <v>7</v>
       </c>
       <c r="B319" t="s">
-        <v>144</v>
-      </c>
-      <c r="C319" t="s">
-        <v>23</v>
+        <v>615</v>
       </c>
       <c r="D319" t="s">
-        <v>145</v>
+        <v>616</v>
       </c>
       <c r="E319" t="s">
-        <v>1155</v>
+        <v>1045</v>
       </c>
       <c r="F319" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G319" t="s">
         <v>11</v>
@@ -10571,19 +10721,19 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B320" t="s">
-        <v>154</v>
+        <v>617</v>
       </c>
       <c r="D320" t="s">
-        <v>155</v>
+        <v>618</v>
       </c>
       <c r="E320" t="s">
-        <v>1156</v>
+        <v>1046</v>
       </c>
       <c r="F320" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G320" t="s">
         <v>11</v>
@@ -10594,16 +10744,16 @@
         <v>7</v>
       </c>
       <c r="B321" t="s">
-        <v>818</v>
+        <v>619</v>
       </c>
       <c r="D321" t="s">
-        <v>819</v>
+        <v>620</v>
       </c>
       <c r="E321" t="s">
-        <v>1157</v>
+        <v>1047</v>
       </c>
       <c r="F321" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G321" t="s">
         <v>11</v>
@@ -10614,16 +10764,16 @@
         <v>7</v>
       </c>
       <c r="B322" t="s">
-        <v>160</v>
+        <v>621</v>
       </c>
       <c r="D322" t="s">
-        <v>161</v>
+        <v>622</v>
       </c>
       <c r="E322" t="s">
-        <v>1158</v>
+        <v>1048</v>
       </c>
       <c r="F322" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G322" t="s">
         <v>11</v>
@@ -10634,16 +10784,16 @@
         <v>7</v>
       </c>
       <c r="B323" t="s">
-        <v>166</v>
+        <v>623</v>
       </c>
       <c r="D323" t="s">
-        <v>167</v>
+        <v>624</v>
       </c>
       <c r="E323" t="s">
-        <v>1159</v>
+        <v>1049</v>
       </c>
       <c r="F323" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G323" t="s">
         <v>11</v>
@@ -10654,16 +10804,16 @@
         <v>7</v>
       </c>
       <c r="B324" t="s">
-        <v>168</v>
+        <v>625</v>
       </c>
       <c r="D324" t="s">
-        <v>169</v>
+        <v>626</v>
       </c>
       <c r="E324" t="s">
-        <v>1160</v>
+        <v>1050</v>
       </c>
       <c r="F324" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G324" t="s">
         <v>11</v>
@@ -10671,16 +10821,16 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B325" t="s">
-        <v>176</v>
+        <v>627</v>
       </c>
       <c r="D325" t="s">
-        <v>177</v>
+        <v>628</v>
       </c>
       <c r="E325" t="s">
-        <v>1161</v>
+        <v>1228</v>
       </c>
       <c r="F325" t="s">
         <v>17</v>
@@ -10694,19 +10844,16 @@
         <v>7</v>
       </c>
       <c r="B326" t="s">
-        <v>182</v>
-      </c>
-      <c r="C326" t="s">
-        <v>23</v>
+        <v>629</v>
       </c>
       <c r="D326" t="s">
-        <v>183</v>
+        <v>630</v>
       </c>
       <c r="E326" t="s">
-        <v>1162</v>
+        <v>1051</v>
       </c>
       <c r="F326" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G326" t="s">
         <v>11</v>
@@ -10717,16 +10864,16 @@
         <v>7</v>
       </c>
       <c r="B327" t="s">
-        <v>820</v>
+        <v>631</v>
       </c>
       <c r="D327" t="s">
-        <v>821</v>
+        <v>632</v>
       </c>
       <c r="E327" t="s">
-        <v>1163</v>
+        <v>1052</v>
       </c>
       <c r="F327" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G327" t="s">
         <v>11</v>
@@ -10737,16 +10884,16 @@
         <v>7</v>
       </c>
       <c r="B328" t="s">
-        <v>822</v>
+        <v>633</v>
       </c>
       <c r="D328" t="s">
-        <v>823</v>
+        <v>634</v>
       </c>
       <c r="E328" t="s">
-        <v>1164</v>
+        <v>1053</v>
       </c>
       <c r="F328" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G328" t="s">
         <v>11</v>
@@ -10757,16 +10904,16 @@
         <v>7</v>
       </c>
       <c r="B329" t="s">
-        <v>224</v>
+        <v>635</v>
       </c>
       <c r="C329" t="s">
         <v>23</v>
       </c>
       <c r="D329" t="s">
-        <v>225</v>
+        <v>636</v>
       </c>
       <c r="E329" t="s">
-        <v>1165</v>
+        <v>1229</v>
       </c>
       <c r="F329" t="s">
         <v>17</v>
@@ -10780,19 +10927,16 @@
         <v>7</v>
       </c>
       <c r="B330" t="s">
-        <v>226</v>
-      </c>
-      <c r="C330" t="s">
-        <v>23</v>
+        <v>637</v>
       </c>
       <c r="D330" t="s">
-        <v>227</v>
+        <v>638</v>
       </c>
       <c r="E330" t="s">
-        <v>1166</v>
+        <v>1054</v>
       </c>
       <c r="F330" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G330" t="s">
         <v>11</v>
@@ -10803,19 +10947,16 @@
         <v>7</v>
       </c>
       <c r="B331" t="s">
-        <v>228</v>
-      </c>
-      <c r="C331" t="s">
-        <v>23</v>
+        <v>639</v>
       </c>
       <c r="D331" t="s">
-        <v>229</v>
+        <v>640</v>
       </c>
       <c r="E331" t="s">
-        <v>1167</v>
+        <v>1055</v>
       </c>
       <c r="F331" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G331" t="s">
         <v>11</v>
@@ -10826,13 +10967,13 @@
         <v>7</v>
       </c>
       <c r="B332" t="s">
-        <v>238</v>
+        <v>641</v>
       </c>
       <c r="D332" t="s">
-        <v>239</v>
+        <v>642</v>
       </c>
       <c r="E332" t="s">
-        <v>1168</v>
+        <v>1230</v>
       </c>
       <c r="F332" t="s">
         <v>17</v>
@@ -10843,19 +10984,19 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B333" t="s">
-        <v>248</v>
+        <v>643</v>
       </c>
       <c r="D333" t="s">
-        <v>249</v>
+        <v>644</v>
       </c>
       <c r="E333" t="s">
-        <v>1169</v>
+        <v>1056</v>
       </c>
       <c r="F333" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G333" t="s">
         <v>11</v>
@@ -10866,19 +11007,16 @@
         <v>7</v>
       </c>
       <c r="B334" t="s">
-        <v>256</v>
-      </c>
-      <c r="C334" t="s">
-        <v>23</v>
+        <v>645</v>
       </c>
       <c r="D334" t="s">
-        <v>257</v>
+        <v>646</v>
       </c>
       <c r="E334" t="s">
-        <v>1170</v>
+        <v>1057</v>
       </c>
       <c r="F334" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G334" t="s">
         <v>11</v>
@@ -10889,16 +11027,16 @@
         <v>7</v>
       </c>
       <c r="B335" t="s">
-        <v>258</v>
+        <v>647</v>
       </c>
       <c r="D335" t="s">
-        <v>259</v>
+        <v>648</v>
       </c>
       <c r="E335" t="s">
-        <v>1171</v>
+        <v>1058</v>
       </c>
       <c r="F335" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G335" t="s">
         <v>11</v>
@@ -10909,16 +11047,16 @@
         <v>7</v>
       </c>
       <c r="B336" t="s">
-        <v>262</v>
+        <v>649</v>
       </c>
       <c r="D336" t="s">
-        <v>263</v>
+        <v>650</v>
       </c>
       <c r="E336" t="s">
-        <v>1172</v>
+        <v>1059</v>
       </c>
       <c r="F336" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G336" t="s">
         <v>11</v>
@@ -10929,13 +11067,13 @@
         <v>7</v>
       </c>
       <c r="B337" t="s">
-        <v>264</v>
+        <v>651</v>
       </c>
       <c r="D337" t="s">
-        <v>265</v>
+        <v>652</v>
       </c>
       <c r="E337" t="s">
-        <v>1173</v>
+        <v>1231</v>
       </c>
       <c r="F337" t="s">
         <v>17</v>
@@ -10949,13 +11087,16 @@
         <v>7</v>
       </c>
       <c r="B338" t="s">
-        <v>270</v>
+        <v>653</v>
+      </c>
+      <c r="C338" t="s">
+        <v>23</v>
       </c>
       <c r="D338" t="s">
-        <v>271</v>
+        <v>654</v>
       </c>
       <c r="E338" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="F338" t="s">
         <v>17</v>
@@ -10969,16 +11110,16 @@
         <v>7</v>
       </c>
       <c r="B339" t="s">
-        <v>337</v>
+        <v>655</v>
       </c>
       <c r="D339" t="s">
-        <v>338</v>
+        <v>656</v>
       </c>
       <c r="E339" t="s">
-        <v>1175</v>
+        <v>1060</v>
       </c>
       <c r="F339" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G339" t="s">
         <v>11</v>
@@ -10986,19 +11127,19 @@
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B340" t="s">
-        <v>339</v>
+        <v>657</v>
       </c>
       <c r="D340" t="s">
-        <v>340</v>
+        <v>658</v>
       </c>
       <c r="E340" t="s">
-        <v>1176</v>
+        <v>1061</v>
       </c>
       <c r="F340" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G340" t="s">
         <v>11</v>
@@ -11009,13 +11150,13 @@
         <v>7</v>
       </c>
       <c r="B341" t="s">
-        <v>347</v>
+        <v>659</v>
       </c>
       <c r="D341" t="s">
-        <v>348</v>
+        <v>660</v>
       </c>
       <c r="E341" t="s">
-        <v>1177</v>
+        <v>1232</v>
       </c>
       <c r="F341" t="s">
         <v>17</v>
@@ -11029,16 +11170,16 @@
         <v>7</v>
       </c>
       <c r="B342" t="s">
-        <v>349</v>
+        <v>661</v>
       </c>
       <c r="D342" t="s">
-        <v>350</v>
+        <v>662</v>
       </c>
       <c r="E342" t="s">
-        <v>1178</v>
+        <v>1062</v>
       </c>
       <c r="F342" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G342" t="s">
         <v>11</v>
@@ -11046,22 +11187,19 @@
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B343" t="s">
-        <v>359</v>
-      </c>
-      <c r="C343" t="s">
-        <v>23</v>
+        <v>663</v>
       </c>
       <c r="D343" t="s">
-        <v>360</v>
+        <v>664</v>
       </c>
       <c r="E343" t="s">
-        <v>1179</v>
+        <v>1063</v>
       </c>
       <c r="F343" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G343" t="s">
         <v>11</v>
@@ -11069,22 +11207,19 @@
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B344" t="s">
-        <v>371</v>
-      </c>
-      <c r="C344" t="s">
-        <v>23</v>
+        <v>665</v>
       </c>
       <c r="D344" t="s">
-        <v>372</v>
+        <v>666</v>
       </c>
       <c r="E344" t="s">
-        <v>1177</v>
+        <v>1064</v>
       </c>
       <c r="F344" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G344" t="s">
         <v>11</v>
@@ -11095,13 +11230,16 @@
         <v>7</v>
       </c>
       <c r="B345" t="s">
-        <v>373</v>
+        <v>667</v>
+      </c>
+      <c r="C345" t="s">
+        <v>23</v>
       </c>
       <c r="D345" t="s">
-        <v>374</v>
+        <v>668</v>
       </c>
       <c r="E345" t="s">
-        <v>1180</v>
+        <v>1233</v>
       </c>
       <c r="F345" t="s">
         <v>17</v>
@@ -11115,16 +11253,16 @@
         <v>7</v>
       </c>
       <c r="B346" t="s">
-        <v>379</v>
+        <v>669</v>
       </c>
       <c r="D346" t="s">
-        <v>380</v>
+        <v>670</v>
       </c>
       <c r="E346" t="s">
-        <v>1181</v>
+        <v>1065</v>
       </c>
       <c r="F346" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G346" t="s">
         <v>11</v>
@@ -11132,19 +11270,19 @@
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B347" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
       <c r="D347" t="s">
-        <v>825</v>
+        <v>672</v>
       </c>
       <c r="E347" t="s">
-        <v>1182</v>
+        <v>1066</v>
       </c>
       <c r="F347" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G347" t="s">
         <v>11</v>
@@ -11155,16 +11293,16 @@
         <v>7</v>
       </c>
       <c r="B348" t="s">
-        <v>826</v>
+        <v>673</v>
       </c>
       <c r="D348" t="s">
-        <v>827</v>
+        <v>674</v>
       </c>
       <c r="E348" t="s">
-        <v>1183</v>
+        <v>1067</v>
       </c>
       <c r="F348" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G348" t="s">
         <v>11</v>
@@ -11175,16 +11313,16 @@
         <v>7</v>
       </c>
       <c r="B349" t="s">
-        <v>387</v>
+        <v>675</v>
       </c>
       <c r="D349" t="s">
-        <v>388</v>
+        <v>676</v>
       </c>
       <c r="E349" t="s">
-        <v>1184</v>
+        <v>1068</v>
       </c>
       <c r="F349" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G349" t="s">
         <v>11</v>
@@ -11192,19 +11330,19 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B350" t="s">
-        <v>395</v>
+        <v>677</v>
       </c>
       <c r="D350" t="s">
-        <v>396</v>
+        <v>678</v>
       </c>
       <c r="E350" t="s">
-        <v>1185</v>
+        <v>1069</v>
       </c>
       <c r="F350" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G350" t="s">
         <v>11</v>
@@ -11215,16 +11353,16 @@
         <v>7</v>
       </c>
       <c r="B351" t="s">
-        <v>397</v>
+        <v>679</v>
       </c>
       <c r="D351" t="s">
-        <v>398</v>
+        <v>680</v>
       </c>
       <c r="E351" t="s">
-        <v>1186</v>
+        <v>1070</v>
       </c>
       <c r="F351" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G351" t="s">
         <v>11</v>
@@ -11235,16 +11373,16 @@
         <v>7</v>
       </c>
       <c r="B352" t="s">
-        <v>830</v>
+        <v>681</v>
       </c>
       <c r="D352" t="s">
-        <v>831</v>
+        <v>682</v>
       </c>
       <c r="E352" t="s">
-        <v>1187</v>
+        <v>1071</v>
       </c>
       <c r="F352" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G352" t="s">
         <v>11</v>
@@ -11252,22 +11390,19 @@
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B353" t="s">
-        <v>417</v>
-      </c>
-      <c r="C353" t="s">
-        <v>23</v>
+        <v>683</v>
       </c>
       <c r="D353" t="s">
-        <v>418</v>
+        <v>684</v>
       </c>
       <c r="E353" t="s">
-        <v>1188</v>
+        <v>1072</v>
       </c>
       <c r="F353" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G353" t="s">
         <v>11</v>
@@ -11278,16 +11413,16 @@
         <v>7</v>
       </c>
       <c r="B354" t="s">
-        <v>425</v>
+        <v>685</v>
       </c>
       <c r="D354" t="s">
-        <v>426</v>
+        <v>686</v>
       </c>
       <c r="E354" t="s">
-        <v>1189</v>
+        <v>1073</v>
       </c>
       <c r="F354" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G354" t="s">
         <v>11</v>
@@ -11295,19 +11430,19 @@
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B355" t="s">
-        <v>427</v>
+        <v>687</v>
       </c>
       <c r="D355" t="s">
-        <v>428</v>
+        <v>688</v>
       </c>
       <c r="E355" t="s">
-        <v>1190</v>
+        <v>1074</v>
       </c>
       <c r="F355" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G355" t="s">
         <v>11</v>
@@ -11318,16 +11453,16 @@
         <v>7</v>
       </c>
       <c r="B356" t="s">
-        <v>429</v>
+        <v>689</v>
       </c>
       <c r="D356" t="s">
-        <v>430</v>
+        <v>690</v>
       </c>
       <c r="E356" t="s">
-        <v>1191</v>
+        <v>1075</v>
       </c>
       <c r="F356" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G356" t="s">
         <v>11</v>
@@ -11335,19 +11470,19 @@
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B357" t="s">
-        <v>447</v>
+        <v>691</v>
       </c>
       <c r="D357" t="s">
-        <v>448</v>
+        <v>692</v>
       </c>
       <c r="E357" t="s">
-        <v>1192</v>
+        <v>1076</v>
       </c>
       <c r="F357" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G357" t="s">
         <v>11</v>
@@ -11355,19 +11490,19 @@
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="B358" t="s">
-        <v>451</v>
+        <v>693</v>
       </c>
       <c r="D358" t="s">
-        <v>452</v>
+        <v>694</v>
       </c>
       <c r="E358" t="s">
-        <v>1193</v>
+        <v>1077</v>
       </c>
       <c r="F358" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G358" t="s">
         <v>11</v>
@@ -11378,19 +11513,16 @@
         <v>7</v>
       </c>
       <c r="B359" t="s">
-        <v>471</v>
-      </c>
-      <c r="C359" t="s">
-        <v>23</v>
+        <v>695</v>
       </c>
       <c r="D359" t="s">
-        <v>472</v>
+        <v>696</v>
       </c>
       <c r="E359" t="s">
-        <v>1194</v>
+        <v>1078</v>
       </c>
       <c r="F359" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G359" t="s">
         <v>11</v>
@@ -11401,16 +11533,16 @@
         <v>7</v>
       </c>
       <c r="B360" t="s">
-        <v>483</v>
+        <v>697</v>
       </c>
       <c r="D360" t="s">
-        <v>484</v>
+        <v>698</v>
       </c>
       <c r="E360" t="s">
-        <v>1195</v>
+        <v>1079</v>
       </c>
       <c r="F360" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G360" t="s">
         <v>11</v>
@@ -11421,16 +11553,16 @@
         <v>7</v>
       </c>
       <c r="B361" t="s">
-        <v>832</v>
+        <v>699</v>
       </c>
       <c r="D361" t="s">
-        <v>833</v>
+        <v>700</v>
       </c>
       <c r="E361" t="s">
-        <v>1196</v>
+        <v>1080</v>
       </c>
       <c r="F361" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G361" t="s">
         <v>11</v>
@@ -11441,16 +11573,16 @@
         <v>7</v>
       </c>
       <c r="B362" t="s">
-        <v>834</v>
+        <v>701</v>
       </c>
       <c r="D362" t="s">
-        <v>835</v>
+        <v>702</v>
       </c>
       <c r="E362" t="s">
-        <v>1197</v>
+        <v>1081</v>
       </c>
       <c r="F362" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G362" t="s">
         <v>11</v>
@@ -11461,16 +11593,16 @@
         <v>7</v>
       </c>
       <c r="B363" t="s">
-        <v>493</v>
+        <v>703</v>
       </c>
       <c r="D363" t="s">
-        <v>494</v>
+        <v>704</v>
       </c>
       <c r="E363" t="s">
-        <v>1198</v>
+        <v>1082</v>
       </c>
       <c r="F363" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G363" t="s">
         <v>11</v>
@@ -11481,19 +11613,16 @@
         <v>7</v>
       </c>
       <c r="B364" t="s">
-        <v>509</v>
-      </c>
-      <c r="C364" t="s">
-        <v>23</v>
+        <v>705</v>
       </c>
       <c r="D364" t="s">
-        <v>510</v>
+        <v>706</v>
       </c>
       <c r="E364" t="s">
-        <v>1199</v>
+        <v>1083</v>
       </c>
       <c r="F364" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G364" t="s">
         <v>11</v>
@@ -11501,22 +11630,19 @@
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B365" t="s">
-        <v>511</v>
-      </c>
-      <c r="C365" t="s">
-        <v>23</v>
+        <v>707</v>
       </c>
       <c r="D365" t="s">
-        <v>512</v>
+        <v>708</v>
       </c>
       <c r="E365" t="s">
-        <v>1200</v>
+        <v>1084</v>
       </c>
       <c r="F365" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G365" t="s">
         <v>11</v>
@@ -11524,19 +11650,19 @@
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B366" t="s">
-        <v>515</v>
+        <v>709</v>
       </c>
       <c r="D366" t="s">
-        <v>516</v>
+        <v>710</v>
       </c>
       <c r="E366" t="s">
-        <v>1201</v>
+        <v>1085</v>
       </c>
       <c r="F366" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G366" t="s">
         <v>11</v>
@@ -11547,19 +11673,16 @@
         <v>7</v>
       </c>
       <c r="B367" t="s">
-        <v>523</v>
-      </c>
-      <c r="C367" t="s">
-        <v>23</v>
+        <v>711</v>
       </c>
       <c r="D367" t="s">
-        <v>524</v>
+        <v>712</v>
       </c>
       <c r="E367" t="s">
-        <v>1202</v>
+        <v>1086</v>
       </c>
       <c r="F367" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G367" t="s">
         <v>11</v>
@@ -11567,22 +11690,19 @@
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B368" t="s">
-        <v>525</v>
-      </c>
-      <c r="C368" t="s">
-        <v>23</v>
+        <v>713</v>
       </c>
       <c r="D368" t="s">
-        <v>526</v>
+        <v>714</v>
       </c>
       <c r="E368" t="s">
-        <v>1203</v>
+        <v>1087</v>
       </c>
       <c r="F368" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G368" t="s">
         <v>11</v>
@@ -11590,22 +11710,19 @@
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B369" t="s">
-        <v>527</v>
-      </c>
-      <c r="C369" t="s">
-        <v>23</v>
+        <v>715</v>
       </c>
       <c r="D369" t="s">
-        <v>528</v>
+        <v>716</v>
       </c>
       <c r="E369" t="s">
-        <v>1204</v>
+        <v>1088</v>
       </c>
       <c r="F369" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G369" t="s">
         <v>11</v>
@@ -11616,16 +11733,13 @@
         <v>7</v>
       </c>
       <c r="B370" t="s">
-        <v>529</v>
-      </c>
-      <c r="C370" t="s">
-        <v>23</v>
+        <v>836</v>
       </c>
       <c r="D370" t="s">
-        <v>530</v>
+        <v>837</v>
       </c>
       <c r="E370" t="s">
-        <v>1205</v>
+        <v>1234</v>
       </c>
       <c r="F370" t="s">
         <v>17</v>
@@ -11639,13 +11753,16 @@
         <v>7</v>
       </c>
       <c r="B371" t="s">
-        <v>836</v>
+        <v>717</v>
+      </c>
+      <c r="C371" t="s">
+        <v>23</v>
       </c>
       <c r="D371" t="s">
-        <v>837</v>
+        <v>718</v>
       </c>
       <c r="E371" t="s">
-        <v>1206</v>
+        <v>1235</v>
       </c>
       <c r="F371" t="s">
         <v>17</v>
@@ -11659,16 +11776,16 @@
         <v>7</v>
       </c>
       <c r="B372" t="s">
-        <v>533</v>
+        <v>719</v>
       </c>
       <c r="D372" t="s">
-        <v>534</v>
+        <v>720</v>
       </c>
       <c r="E372" t="s">
-        <v>1207</v>
+        <v>1089</v>
       </c>
       <c r="F372" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G372" t="s">
         <v>11</v>
@@ -11679,16 +11796,13 @@
         <v>7</v>
       </c>
       <c r="B373" t="s">
-        <v>535</v>
-      </c>
-      <c r="C373" t="s">
-        <v>23</v>
+        <v>721</v>
       </c>
       <c r="D373" t="s">
-        <v>536</v>
+        <v>722</v>
       </c>
       <c r="E373" t="s">
-        <v>1208</v>
+        <v>1236</v>
       </c>
       <c r="F373" t="s">
         <v>17</v>
@@ -11702,19 +11816,16 @@
         <v>7</v>
       </c>
       <c r="B374" t="s">
-        <v>537</v>
-      </c>
-      <c r="C374" t="s">
-        <v>23</v>
+        <v>723</v>
       </c>
       <c r="D374" t="s">
-        <v>538</v>
+        <v>724</v>
       </c>
       <c r="E374" t="s">
-        <v>1209</v>
+        <v>1090</v>
       </c>
       <c r="F374" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G374" t="s">
         <v>11</v>
@@ -11725,19 +11836,16 @@
         <v>7</v>
       </c>
       <c r="B375" t="s">
-        <v>539</v>
-      </c>
-      <c r="C375" t="s">
-        <v>23</v>
+        <v>725</v>
       </c>
       <c r="D375" t="s">
-        <v>540</v>
+        <v>726</v>
       </c>
       <c r="E375" t="s">
-        <v>1210</v>
+        <v>1091</v>
       </c>
       <c r="F375" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G375" t="s">
         <v>11</v>
@@ -11748,19 +11856,16 @@
         <v>7</v>
       </c>
       <c r="B376" t="s">
-        <v>541</v>
-      </c>
-      <c r="C376" t="s">
-        <v>23</v>
+        <v>727</v>
       </c>
       <c r="D376" t="s">
-        <v>542</v>
+        <v>728</v>
       </c>
       <c r="E376" t="s">
-        <v>1211</v>
+        <v>1092</v>
       </c>
       <c r="F376" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G376" t="s">
         <v>11</v>
@@ -11771,19 +11876,16 @@
         <v>7</v>
       </c>
       <c r="B377" t="s">
-        <v>543</v>
-      </c>
-      <c r="C377" t="s">
-        <v>23</v>
+        <v>729</v>
       </c>
       <c r="D377" t="s">
-        <v>544</v>
+        <v>730</v>
       </c>
       <c r="E377" t="s">
-        <v>1212</v>
+        <v>1093</v>
       </c>
       <c r="F377" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G377" t="s">
         <v>11</v>
@@ -11791,22 +11893,19 @@
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B378" t="s">
-        <v>545</v>
-      </c>
-      <c r="C378" t="s">
-        <v>23</v>
+        <v>731</v>
       </c>
       <c r="D378" t="s">
-        <v>546</v>
+        <v>732</v>
       </c>
       <c r="E378" t="s">
-        <v>1213</v>
+        <v>1094</v>
       </c>
       <c r="F378" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G378" t="s">
         <v>11</v>
@@ -11817,19 +11916,16 @@
         <v>7</v>
       </c>
       <c r="B379" t="s">
-        <v>547</v>
-      </c>
-      <c r="C379" t="s">
-        <v>23</v>
+        <v>733</v>
       </c>
       <c r="D379" t="s">
-        <v>548</v>
+        <v>734</v>
       </c>
       <c r="E379" t="s">
-        <v>1214</v>
+        <v>1095</v>
       </c>
       <c r="F379" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G379" t="s">
         <v>11</v>
@@ -11840,19 +11936,16 @@
         <v>7</v>
       </c>
       <c r="B380" t="s">
-        <v>549</v>
-      </c>
-      <c r="C380" t="s">
-        <v>23</v>
+        <v>735</v>
       </c>
       <c r="D380" t="s">
-        <v>550</v>
+        <v>736</v>
       </c>
       <c r="E380" t="s">
-        <v>1215</v>
+        <v>1096</v>
       </c>
       <c r="F380" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G380" t="s">
         <v>11</v>
@@ -11863,19 +11956,16 @@
         <v>7</v>
       </c>
       <c r="B381" t="s">
-        <v>551</v>
-      </c>
-      <c r="C381" t="s">
-        <v>23</v>
+        <v>737</v>
       </c>
       <c r="D381" t="s">
-        <v>552</v>
+        <v>738</v>
       </c>
       <c r="E381" t="s">
-        <v>1216</v>
+        <v>1097</v>
       </c>
       <c r="F381" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G381" t="s">
         <v>11</v>
@@ -11883,19 +11973,19 @@
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B382" t="s">
-        <v>553</v>
+        <v>739</v>
       </c>
       <c r="D382" t="s">
-        <v>554</v>
+        <v>740</v>
       </c>
       <c r="E382" t="s">
-        <v>1217</v>
+        <v>1098</v>
       </c>
       <c r="F382" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G382" t="s">
         <v>11</v>
@@ -11906,19 +11996,16 @@
         <v>7</v>
       </c>
       <c r="B383" t="s">
-        <v>555</v>
-      </c>
-      <c r="C383" t="s">
-        <v>23</v>
+        <v>741</v>
       </c>
       <c r="D383" t="s">
-        <v>556</v>
+        <v>742</v>
       </c>
       <c r="E383" t="s">
-        <v>1218</v>
+        <v>1099</v>
       </c>
       <c r="F383" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G383" t="s">
         <v>11</v>
@@ -11929,19 +12016,16 @@
         <v>7</v>
       </c>
       <c r="B384" t="s">
-        <v>557</v>
-      </c>
-      <c r="C384" t="s">
-        <v>23</v>
+        <v>743</v>
       </c>
       <c r="D384" t="s">
-        <v>558</v>
+        <v>744</v>
       </c>
       <c r="E384" t="s">
-        <v>1219</v>
+        <v>1100</v>
       </c>
       <c r="F384" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G384" t="s">
         <v>11</v>
@@ -11952,16 +12036,13 @@
         <v>7</v>
       </c>
       <c r="B385" t="s">
-        <v>559</v>
-      </c>
-      <c r="C385" t="s">
-        <v>23</v>
+        <v>745</v>
       </c>
       <c r="D385" t="s">
-        <v>560</v>
+        <v>746</v>
       </c>
       <c r="E385" t="s">
-        <v>1220</v>
+        <v>1237</v>
       </c>
       <c r="F385" t="s">
         <v>17</v>
@@ -11975,19 +12056,16 @@
         <v>7</v>
       </c>
       <c r="B386" t="s">
-        <v>561</v>
-      </c>
-      <c r="C386" t="s">
-        <v>23</v>
+        <v>747</v>
       </c>
       <c r="D386" t="s">
-        <v>562</v>
+        <v>748</v>
       </c>
       <c r="E386" t="s">
-        <v>1221</v>
+        <v>1101</v>
       </c>
       <c r="F386" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G386" t="s">
         <v>11</v>
@@ -11998,19 +12076,16 @@
         <v>7</v>
       </c>
       <c r="B387" t="s">
-        <v>563</v>
-      </c>
-      <c r="C387" t="s">
-        <v>23</v>
+        <v>749</v>
       </c>
       <c r="D387" t="s">
-        <v>564</v>
+        <v>750</v>
       </c>
       <c r="E387" t="s">
-        <v>1222</v>
+        <v>1102</v>
       </c>
       <c r="F387" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G387" t="s">
         <v>11</v>
@@ -12018,22 +12093,19 @@
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B388" t="s">
-        <v>565</v>
-      </c>
-      <c r="C388" t="s">
-        <v>23</v>
+        <v>751</v>
       </c>
       <c r="D388" t="s">
-        <v>566</v>
+        <v>752</v>
       </c>
       <c r="E388" t="s">
-        <v>1223</v>
+        <v>1103</v>
       </c>
       <c r="F388" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G388" t="s">
         <v>11</v>
@@ -12044,19 +12116,16 @@
         <v>7</v>
       </c>
       <c r="B389" t="s">
-        <v>567</v>
-      </c>
-      <c r="C389" t="s">
-        <v>23</v>
+        <v>753</v>
       </c>
       <c r="D389" t="s">
-        <v>568</v>
+        <v>754</v>
       </c>
       <c r="E389" t="s">
-        <v>1224</v>
+        <v>1104</v>
       </c>
       <c r="F389" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G389" t="s">
         <v>11</v>
@@ -12067,19 +12136,16 @@
         <v>7</v>
       </c>
       <c r="B390" t="s">
-        <v>569</v>
-      </c>
-      <c r="C390" t="s">
-        <v>23</v>
+        <v>755</v>
       </c>
       <c r="D390" t="s">
-        <v>570</v>
+        <v>756</v>
       </c>
       <c r="E390" t="s">
-        <v>1225</v>
+        <v>1105</v>
       </c>
       <c r="F390" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G390" t="s">
         <v>11</v>
@@ -12090,19 +12156,16 @@
         <v>7</v>
       </c>
       <c r="B391" t="s">
-        <v>571</v>
-      </c>
-      <c r="C391" t="s">
-        <v>23</v>
+        <v>757</v>
       </c>
       <c r="D391" t="s">
-        <v>572</v>
+        <v>758</v>
       </c>
       <c r="E391" t="s">
-        <v>1226</v>
+        <v>1106</v>
       </c>
       <c r="F391" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G391" t="s">
         <v>11</v>
@@ -12113,19 +12176,16 @@
         <v>7</v>
       </c>
       <c r="B392" t="s">
-        <v>577</v>
-      </c>
-      <c r="C392" t="s">
-        <v>23</v>
+        <v>759</v>
       </c>
       <c r="D392" t="s">
-        <v>578</v>
+        <v>760</v>
       </c>
       <c r="E392" t="s">
-        <v>1227</v>
+        <v>1107</v>
       </c>
       <c r="F392" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G392" t="s">
         <v>11</v>
@@ -12136,16 +12196,13 @@
         <v>7</v>
       </c>
       <c r="B393" t="s">
-        <v>589</v>
-      </c>
-      <c r="C393" t="s">
-        <v>23</v>
+        <v>761</v>
       </c>
       <c r="D393" t="s">
-        <v>590</v>
+        <v>762</v>
       </c>
       <c r="E393" t="s">
-        <v>1228</v>
+        <v>1238</v>
       </c>
       <c r="F393" t="s">
         <v>17</v>
@@ -12156,19 +12213,19 @@
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B394" t="s">
-        <v>603</v>
+        <v>763</v>
       </c>
       <c r="D394" t="s">
-        <v>604</v>
+        <v>764</v>
       </c>
       <c r="E394" t="s">
-        <v>1229</v>
+        <v>1108</v>
       </c>
       <c r="F394" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G394" t="s">
         <v>11</v>
@@ -12179,16 +12236,16 @@
         <v>7</v>
       </c>
       <c r="B395" t="s">
-        <v>607</v>
+        <v>765</v>
       </c>
       <c r="C395" t="s">
-        <v>23</v>
+        <v>766</v>
       </c>
       <c r="D395" t="s">
-        <v>608</v>
+        <v>767</v>
       </c>
       <c r="E395" t="s">
-        <v>1230</v>
+        <v>1239</v>
       </c>
       <c r="F395" t="s">
         <v>17</v>
@@ -12199,19 +12256,19 @@
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>7</v>
+        <v>768</v>
       </c>
       <c r="B396" t="s">
-        <v>629</v>
+        <v>769</v>
       </c>
       <c r="D396" t="s">
-        <v>630</v>
+        <v>770</v>
       </c>
       <c r="E396" t="s">
-        <v>1231</v>
+        <v>1109</v>
       </c>
       <c r="F396" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G396" t="s">
         <v>11</v>
@@ -12222,16 +12279,16 @@
         <v>7</v>
       </c>
       <c r="B397" t="s">
-        <v>637</v>
+        <v>771</v>
       </c>
       <c r="C397" t="s">
         <v>23</v>
       </c>
       <c r="D397" t="s">
-        <v>638</v>
+        <v>838</v>
       </c>
       <c r="E397" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="F397" t="s">
         <v>17</v>
@@ -12245,16 +12302,16 @@
         <v>7</v>
       </c>
       <c r="B398" t="s">
-        <v>643</v>
+        <v>772</v>
       </c>
       <c r="D398" t="s">
-        <v>644</v>
+        <v>773</v>
       </c>
       <c r="E398" t="s">
-        <v>1233</v>
+        <v>1110</v>
       </c>
       <c r="F398" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G398" t="s">
         <v>11</v>
@@ -12265,16 +12322,16 @@
         <v>7</v>
       </c>
       <c r="B399" t="s">
-        <v>653</v>
+        <v>774</v>
       </c>
       <c r="D399" t="s">
-        <v>654</v>
+        <v>775</v>
       </c>
       <c r="E399" t="s">
-        <v>1234</v>
+        <v>1111</v>
       </c>
       <c r="F399" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G399" t="s">
         <v>11</v>
@@ -12285,19 +12342,16 @@
         <v>7</v>
       </c>
       <c r="B400" t="s">
-        <v>655</v>
-      </c>
-      <c r="C400" t="s">
-        <v>23</v>
+        <v>776</v>
       </c>
       <c r="D400" t="s">
-        <v>656</v>
+        <v>777</v>
       </c>
       <c r="E400" t="s">
-        <v>1171</v>
+        <v>1112</v>
       </c>
       <c r="F400" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G400" t="s">
         <v>11</v>
@@ -12305,19 +12359,19 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B401" t="s">
-        <v>661</v>
+        <v>778</v>
       </c>
       <c r="D401" t="s">
-        <v>662</v>
+        <v>779</v>
       </c>
       <c r="E401" t="s">
-        <v>1235</v>
+        <v>1113</v>
       </c>
       <c r="F401" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G401" t="s">
         <v>11</v>
@@ -12328,19 +12382,16 @@
         <v>7</v>
       </c>
       <c r="B402" t="s">
-        <v>669</v>
-      </c>
-      <c r="C402" t="s">
-        <v>23</v>
+        <v>780</v>
       </c>
       <c r="D402" t="s">
-        <v>670</v>
+        <v>781</v>
       </c>
       <c r="E402" t="s">
-        <v>1236</v>
+        <v>1114</v>
       </c>
       <c r="F402" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G402" t="s">
         <v>11</v>
@@ -12348,19 +12399,19 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B403" t="s">
-        <v>838</v>
+        <v>782</v>
       </c>
       <c r="D403" t="s">
-        <v>839</v>
+        <v>783</v>
       </c>
       <c r="E403" t="s">
-        <v>1237</v>
+        <v>1115</v>
       </c>
       <c r="F403" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G403" t="s">
         <v>11</v>
@@ -12371,19 +12422,16 @@
         <v>7</v>
       </c>
       <c r="B404" t="s">
-        <v>719</v>
-      </c>
-      <c r="C404" t="s">
-        <v>23</v>
+        <v>784</v>
       </c>
       <c r="D404" t="s">
-        <v>720</v>
+        <v>785</v>
       </c>
       <c r="E404" t="s">
-        <v>1238</v>
+        <v>1116</v>
       </c>
       <c r="F404" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G404" t="s">
         <v>11</v>
@@ -12394,13 +12442,16 @@
         <v>7</v>
       </c>
       <c r="B405" t="s">
-        <v>723</v>
+        <v>786</v>
+      </c>
+      <c r="C405" t="s">
+        <v>787</v>
       </c>
       <c r="D405" t="s">
-        <v>724</v>
+        <v>788</v>
       </c>
       <c r="E405" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F405" t="s">
         <v>17</v>
@@ -12414,16 +12465,16 @@
         <v>7</v>
       </c>
       <c r="B406" t="s">
-        <v>747</v>
+        <v>789</v>
       </c>
       <c r="D406" t="s">
-        <v>748</v>
+        <v>790</v>
       </c>
       <c r="E406" t="s">
-        <v>1240</v>
+        <v>1117</v>
       </c>
       <c r="F406" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G406" t="s">
         <v>11</v>
@@ -12431,19 +12482,19 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B407" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
       <c r="D407" t="s">
-        <v>764</v>
+        <v>792</v>
       </c>
       <c r="E407" t="s">
-        <v>1241</v>
+        <v>1118</v>
       </c>
       <c r="F407" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G407" t="s">
         <v>11</v>
@@ -12451,22 +12502,19 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B408" t="s">
-        <v>767</v>
-      </c>
-      <c r="C408" t="s">
-        <v>768</v>
+        <v>793</v>
       </c>
       <c r="D408" t="s">
-        <v>769</v>
+        <v>794</v>
       </c>
       <c r="E408" t="s">
-        <v>1242</v>
+        <v>1119</v>
       </c>
       <c r="F408" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G408" t="s">
         <v>11</v>
@@ -12474,22 +12522,19 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B409" t="s">
-        <v>773</v>
-      </c>
-      <c r="C409" t="s">
-        <v>23</v>
+        <v>795</v>
       </c>
       <c r="D409" t="s">
-        <v>840</v>
+        <v>796</v>
       </c>
       <c r="E409" t="s">
-        <v>1243</v>
+        <v>1120</v>
       </c>
       <c r="F409" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G409" t="s">
         <v>11</v>
@@ -12497,24 +12542,121 @@
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B410" t="s">
-        <v>788</v>
-      </c>
-      <c r="C410" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="D410" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="E410" t="s">
-        <v>1241</v>
+        <v>1121</v>
       </c>
       <c r="F410" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G410" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>30</v>
+      </c>
+      <c r="B411" t="s">
+        <v>799</v>
+      </c>
+      <c r="D411" t="s">
+        <v>800</v>
+      </c>
+      <c r="E411" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F411" t="s">
+        <v>10</v>
+      </c>
+      <c r="G411" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>7</v>
+      </c>
+      <c r="B412" t="s">
+        <v>801</v>
+      </c>
+      <c r="D412" t="s">
+        <v>802</v>
+      </c>
+      <c r="E412" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F412" t="s">
+        <v>10</v>
+      </c>
+      <c r="G412" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>30</v>
+      </c>
+      <c r="B413" t="s">
+        <v>803</v>
+      </c>
+      <c r="D413" t="s">
+        <v>804</v>
+      </c>
+      <c r="E413" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F413" t="s">
+        <v>10</v>
+      </c>
+      <c r="G413" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>7</v>
+      </c>
+      <c r="B414" t="s">
+        <v>805</v>
+      </c>
+      <c r="D414" t="s">
+        <v>806</v>
+      </c>
+      <c r="E414" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F414" t="s">
+        <v>10</v>
+      </c>
+      <c r="G414" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>7</v>
+      </c>
+      <c r="B415" t="s">
+        <v>807</v>
+      </c>
+      <c r="D415" t="s">
+        <v>808</v>
+      </c>
+      <c r="E415" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F415" t="s">
+        <v>10</v>
+      </c>
+      <c r="G415" t="s">
         <v>11</v>
       </c>
     </row>
